--- a/data/Mapa_das_Desigualdades_Sao_Vicente.xlsx
+++ b/data/Mapa_das_Desigualdades_Sao_Vicente.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="326">
   <si>
     <t>Bairro</t>
   </si>
@@ -123,6 +123,9 @@
     <t>Sem iluminação (%)</t>
   </si>
   <si>
+    <t>Sem rampa p/ cadeirante (%)</t>
+  </si>
+  <si>
     <t>Área continental (rural)</t>
   </si>
   <si>
@@ -318,6 +321,9 @@
     <t>Associação fraca: cresce onde a renda é menor.</t>
   </si>
   <si>
+    <t>% sem rampa para cadeirante</t>
+  </si>
+  <si>
     <t>paradas por km²</t>
   </si>
   <si>
@@ -745,6 +751,18 @@
   </si>
   <si>
     <t>pct_sem_il</t>
+  </si>
+  <si>
+    <t>pct_sem_rampa</t>
+  </si>
+  <si>
+    <t>pct_sem_ra</t>
+  </si>
+  <si>
+    <t>domicilios_entorno</t>
+  </si>
+  <si>
+    <t>domicilio1</t>
   </si>
   <si>
     <t>pct_via_pavim</t>
@@ -1404,7 +1422,7 @@
   <sheetPr>
     <tabColor rgb="FF007A4A"/>
   </sheetPr>
-  <dimension ref="A1:AI31"/>
+  <dimension ref="A1:AJ31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1439,9 +1457,10 @@
     <col min="32" max="33" width="12" style="4" customWidth="1"/>
     <col min="34" max="34" width="11" style="4" customWidth="1"/>
     <col min="35" max="35" width="12" style="4" customWidth="1"/>
+    <col min="36" max="36" width="14" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:35" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="34" customHeight="1" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1547,13 +1566,16 @@
       <c r="AI1" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ1" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="11">
         <v>555</v>
@@ -1607,7 +1629,7 @@
         <v>2</v>
       </c>
       <c r="T2" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U2" s="10"/>
       <c r="V2" s="10">
@@ -1626,13 +1648,14 @@
       <c r="AG2" s="14"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="14"/>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ2" s="14"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1">
         <v>7536</v>
@@ -1686,10 +1709,10 @@
         <v>4</v>
       </c>
       <c r="T3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V3">
         <v>19</v>
@@ -1703,7 +1726,9 @@
       <c r="Y3" s="4">
         <v>0</v>
       </c>
-      <c r="Z3" s="4"/>
+      <c r="Z3" s="4">
+        <v>99.89</v>
+      </c>
       <c r="AA3" s="4">
         <v>99.77</v>
       </c>
@@ -1731,13 +1756,16 @@
       <c r="AI3" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ3" s="4">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11">
         <v>9992</v>
@@ -1791,10 +1819,10 @@
         <v>1</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" s="10">
         <v>0</v>
@@ -1808,7 +1836,9 @@
       <c r="Y4" s="14">
         <v>0</v>
       </c>
-      <c r="Z4" s="14"/>
+      <c r="Z4" s="14">
+        <v>100</v>
+      </c>
       <c r="AA4" s="14">
         <v>99.92</v>
       </c>
@@ -1836,13 +1866,16 @@
       <c r="AI4" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ4" s="14">
+        <v>72.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1">
         <v>14903</v>
@@ -1896,10 +1929,10 @@
         <v>7</v>
       </c>
       <c r="T5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V5">
         <v>44</v>
@@ -1913,7 +1946,9 @@
       <c r="Y5" s="4">
         <v>0.1</v>
       </c>
-      <c r="Z5" s="4"/>
+      <c r="Z5" s="4">
+        <v>99.98</v>
+      </c>
       <c r="AA5" s="4">
         <v>99.79</v>
       </c>
@@ -1930,24 +1965,27 @@
         <v>19.05</v>
       </c>
       <c r="AF5" s="4">
-        <v>9.26</v>
+        <v>6.37</v>
       </c>
       <c r="AG5" s="4">
-        <v>59.58</v>
+        <v>61.48</v>
       </c>
       <c r="AH5" s="4">
-        <v>6.44</v>
+        <v>6.64</v>
       </c>
       <c r="AI5" s="4">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+      <c r="AJ5" s="4">
+        <v>78.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="11">
         <v>8870</v>
@@ -2001,10 +2039,10 @@
         <v>6</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V6" s="10">
         <v>16</v>
@@ -2018,7 +2056,9 @@
       <c r="Y6" s="14">
         <v>0</v>
       </c>
-      <c r="Z6" s="14"/>
+      <c r="Z6" s="14">
+        <v>99.95</v>
+      </c>
       <c r="AA6" s="14">
         <v>99.76</v>
       </c>
@@ -2046,13 +2086,16 @@
       <c r="AI6" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ6" s="14">
+        <v>23.87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1">
         <v>31596</v>
@@ -2106,10 +2149,10 @@
         <v>13</v>
       </c>
       <c r="T7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V7">
         <v>58</v>
@@ -2123,7 +2166,9 @@
       <c r="Y7" s="4">
         <v>3.6</v>
       </c>
-      <c r="Z7" s="4"/>
+      <c r="Z7" s="4">
+        <v>99.75</v>
+      </c>
       <c r="AA7" s="4">
         <v>99.88</v>
       </c>
@@ -2151,13 +2196,16 @@
       <c r="AI7" s="4">
         <v>1.18</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ7" s="4">
+        <v>56.59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="11">
         <v>8644</v>
@@ -2211,7 +2259,7 @@
         <v>12</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U8" s="10"/>
       <c r="V8" s="10">
@@ -2226,7 +2274,9 @@
       <c r="Y8" s="14">
         <v>2.49</v>
       </c>
-      <c r="Z8" s="14"/>
+      <c r="Z8" s="14">
+        <v>99.78</v>
+      </c>
       <c r="AA8" s="14">
         <v>99.87</v>
       </c>
@@ -2254,13 +2304,16 @@
       <c r="AI8" s="14">
         <v>2.37</v>
       </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ8" s="14">
+        <v>84.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1">
         <v>11360</v>
@@ -2314,10 +2367,10 @@
         <v>4</v>
       </c>
       <c r="T9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V9">
         <v>16</v>
@@ -2331,7 +2384,9 @@
       <c r="Y9" s="4">
         <v>0.08</v>
       </c>
-      <c r="Z9" s="4"/>
+      <c r="Z9" s="4">
+        <v>100</v>
+      </c>
       <c r="AA9" s="4">
         <v>99.8</v>
       </c>
@@ -2348,24 +2403,27 @@
         <v>30.5</v>
       </c>
       <c r="AF9" s="4">
-        <v>2.18</v>
+        <v>0.24</v>
       </c>
       <c r="AG9" s="4">
-        <v>20.02</v>
+        <v>20.41</v>
       </c>
       <c r="AH9" s="4">
-        <v>7.61</v>
+        <v>7.76</v>
       </c>
       <c r="AI9" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ9" s="4">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="11">
         <v>11685</v>
@@ -2419,10 +2477,10 @@
         <v>29</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V10" s="10">
         <v>33</v>
@@ -2436,7 +2494,9 @@
       <c r="Y10" s="14">
         <v>0</v>
       </c>
-      <c r="Z10" s="14"/>
+      <c r="Z10" s="14">
+        <v>99.97</v>
+      </c>
       <c r="AA10" s="14">
         <v>100</v>
       </c>
@@ -2464,13 +2524,16 @@
       <c r="AI10" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ10" s="14">
+        <v>86.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1">
         <v>8792</v>
@@ -2524,10 +2587,10 @@
         <v>7</v>
       </c>
       <c r="T11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2541,7 +2604,9 @@
       <c r="Y11" s="4">
         <v>1.01</v>
       </c>
-      <c r="Z11" s="4"/>
+      <c r="Z11" s="4">
+        <v>99.91</v>
+      </c>
       <c r="AA11" s="4">
         <v>98.88</v>
       </c>
@@ -2558,24 +2623,27 @@
         <v>30.03</v>
       </c>
       <c r="AF11" s="4">
-        <v>9.82</v>
+        <v>3.3</v>
       </c>
       <c r="AG11" s="4">
-        <v>17.44</v>
+        <v>18.7</v>
       </c>
       <c r="AH11" s="4">
-        <v>5.62</v>
+        <v>6.03</v>
       </c>
       <c r="AI11" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ11" s="4">
+        <v>57.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="11">
         <v>5694</v>
@@ -2629,10 +2697,10 @@
         <v>5</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V12" s="10">
         <v>14</v>
@@ -2646,7 +2714,9 @@
       <c r="Y12" s="14">
         <v>0.56</v>
       </c>
-      <c r="Z12" s="14"/>
+      <c r="Z12" s="14">
+        <v>99.49</v>
+      </c>
       <c r="AA12" s="14">
         <v>99.95</v>
       </c>
@@ -2663,10 +2733,10 @@
         <v>17.6</v>
       </c>
       <c r="AF12" s="14">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="AG12" s="14">
-        <v>9.51</v>
+        <v>9.56</v>
       </c>
       <c r="AH12" s="14">
         <v>0.47</v>
@@ -2674,13 +2744,16 @@
       <c r="AI12" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ12" s="14">
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1">
         <v>3454</v>
@@ -2734,10 +2807,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V13">
         <v>13</v>
@@ -2751,7 +2824,9 @@
       <c r="Y13" s="4">
         <v>0.97</v>
       </c>
-      <c r="Z13" s="4"/>
+      <c r="Z13" s="4">
+        <v>100</v>
+      </c>
       <c r="AA13" s="4">
         <v>99.92</v>
       </c>
@@ -2779,13 +2854,16 @@
       <c r="AI13" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ13" s="4">
+        <v>70.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="11">
         <v>3367</v>
@@ -2839,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V14" s="10">
         <v>13</v>
@@ -2856,7 +2934,9 @@
       <c r="Y14" s="14">
         <v>0.87</v>
       </c>
-      <c r="Z14" s="14"/>
+      <c r="Z14" s="14">
+        <v>100</v>
+      </c>
       <c r="AA14" s="14">
         <v>99.76</v>
       </c>
@@ -2884,13 +2964,16 @@
       <c r="AI14" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ14" s="14">
+        <v>87.71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1">
         <v>24906</v>
@@ -2944,7 +3027,7 @@
         <v>3</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2958,7 +3041,9 @@
       <c r="Y15" s="4">
         <v>13.23</v>
       </c>
-      <c r="Z15" s="4"/>
+      <c r="Z15" s="4">
+        <v>99.6</v>
+      </c>
       <c r="AA15" s="4">
         <v>99.48</v>
       </c>
@@ -2975,24 +3060,27 @@
         <v>9.74</v>
       </c>
       <c r="AF15" s="4">
-        <v>36.44</v>
+        <v>36.28</v>
       </c>
       <c r="AG15" s="4">
-        <v>52.32</v>
+        <v>52.45</v>
       </c>
       <c r="AH15" s="4">
-        <v>31.22</v>
+        <v>31.3</v>
       </c>
       <c r="AI15" s="4">
-        <v>15.94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>15.98</v>
+      </c>
+      <c r="AJ15" s="4">
+        <v>62.94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="11">
         <v>20472</v>
@@ -3046,10 +3134,10 @@
         <v>2</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V16" s="10">
         <v>1</v>
@@ -3063,7 +3151,9 @@
       <c r="Y16" s="14">
         <v>0.12</v>
       </c>
-      <c r="Z16" s="14"/>
+      <c r="Z16" s="14">
+        <v>99.9</v>
+      </c>
       <c r="AA16" s="14">
         <v>99.57</v>
       </c>
@@ -3080,7 +3170,7 @@
         <v>9.84</v>
       </c>
       <c r="AF16" s="14">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="AG16" s="14">
         <v>30.2</v>
@@ -3091,13 +3181,16 @@
       <c r="AI16" s="14">
         <v>9.67</v>
       </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ16" s="14">
+        <v>65.54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1">
         <v>28265</v>
@@ -3151,10 +3244,10 @@
         <v>18</v>
       </c>
       <c r="T17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V17">
         <v>27</v>
@@ -3168,7 +3261,9 @@
       <c r="Y17" s="4">
         <v>14.91</v>
       </c>
-      <c r="Z17" s="4"/>
+      <c r="Z17" s="4">
+        <v>97.85</v>
+      </c>
       <c r="AA17" s="4">
         <v>99.6</v>
       </c>
@@ -3185,24 +3280,27 @@
         <v>13.37</v>
       </c>
       <c r="AF17" s="4">
-        <v>14.42</v>
+        <v>13.22</v>
       </c>
       <c r="AG17" s="4">
-        <v>35.04</v>
+        <v>35.53</v>
       </c>
       <c r="AH17" s="4">
-        <v>18.27</v>
+        <v>18.53</v>
       </c>
       <c r="AI17" s="4">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>1.56</v>
+      </c>
+      <c r="AJ17" s="4">
+        <v>75.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="11">
         <v>4075</v>
@@ -3256,7 +3354,7 @@
         <v>4</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U18" s="10"/>
       <c r="V18" s="10">
@@ -3271,7 +3369,9 @@
       <c r="Y18" s="14">
         <v>7.56</v>
       </c>
-      <c r="Z18" s="14"/>
+      <c r="Z18" s="14">
+        <v>99.93</v>
+      </c>
       <c r="AA18" s="14">
         <v>99.78</v>
       </c>
@@ -3299,13 +3399,16 @@
       <c r="AI18" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ18" s="14">
+        <v>79.71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1">
         <v>14351</v>
@@ -3359,10 +3462,10 @@
         <v>7</v>
       </c>
       <c r="T19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V19">
         <v>31</v>
@@ -3376,7 +3479,9 @@
       <c r="Y19" s="4">
         <v>2.73</v>
       </c>
-      <c r="Z19" s="4"/>
+      <c r="Z19" s="4">
+        <v>99.83</v>
+      </c>
       <c r="AA19" s="4">
         <v>99.68</v>
       </c>
@@ -3393,24 +3498,27 @@
         <v>20.01</v>
       </c>
       <c r="AF19" s="4">
-        <v>7.45</v>
+        <v>6.93</v>
       </c>
       <c r="AG19" s="4">
-        <v>48.03</v>
+        <v>48.3</v>
       </c>
       <c r="AH19" s="4">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ19" s="4">
+        <v>59.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="11">
         <v>13171</v>
@@ -3464,10 +3572,10 @@
         <v>9</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V20" s="10">
         <v>35</v>
@@ -3481,7 +3589,9 @@
       <c r="Y20" s="14">
         <v>6.48</v>
       </c>
-      <c r="Z20" s="14"/>
+      <c r="Z20" s="14">
+        <v>99.98</v>
+      </c>
       <c r="AA20" s="14">
         <v>99.98</v>
       </c>
@@ -3509,13 +3619,16 @@
       <c r="AI20" s="14">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ20" s="14">
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1">
         <v>11980</v>
@@ -3569,7 +3682,7 @@
         <v>8</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3583,7 +3696,9 @@
       <c r="Y21" s="4">
         <v>0.48</v>
       </c>
-      <c r="Z21" s="4"/>
+      <c r="Z21" s="4">
+        <v>99.88</v>
+      </c>
       <c r="AA21" s="4">
         <v>99.86</v>
       </c>
@@ -3600,24 +3715,27 @@
         <v>16.14</v>
       </c>
       <c r="AF21" s="4">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AG21" s="4">
-        <v>11.45</v>
+        <v>11.47</v>
       </c>
       <c r="AH21" s="4">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="AI21" s="4">
         <v>0.07</v>
       </c>
-    </row>
-    <row r="22" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ21" s="4">
+        <v>86.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" s="11">
         <v>10374</v>
@@ -3671,10 +3789,10 @@
         <v>3</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V22" s="10">
         <v>49</v>
@@ -3688,7 +3806,9 @@
       <c r="Y22" s="14">
         <v>0.13</v>
       </c>
-      <c r="Z22" s="14"/>
+      <c r="Z22" s="14">
+        <v>99.97</v>
+      </c>
       <c r="AA22" s="14">
         <v>99.87</v>
       </c>
@@ -3705,10 +3825,10 @@
         <v>17.88</v>
       </c>
       <c r="AF22" s="14">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AG22" s="14">
-        <v>41.59</v>
+        <v>41.6</v>
       </c>
       <c r="AH22" s="14">
         <v>0</v>
@@ -3716,13 +3836,16 @@
       <c r="AI22" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ22" s="14">
+        <v>65.08</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1">
         <v>11148</v>
@@ -3776,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3790,7 +3913,9 @@
       <c r="Y23" s="4">
         <v>26.19</v>
       </c>
-      <c r="Z23" s="4"/>
+      <c r="Z23" s="4">
+        <v>92.92</v>
+      </c>
       <c r="AA23" s="4">
         <v>95.3</v>
       </c>
@@ -3807,24 +3932,27 @@
         <v>7.57</v>
       </c>
       <c r="AF23" s="4">
-        <v>49.35</v>
+        <v>49.24</v>
       </c>
       <c r="AG23" s="4">
-        <v>84.84</v>
+        <v>84.93</v>
       </c>
       <c r="AH23" s="4">
-        <v>41.4</v>
+        <v>41.44</v>
       </c>
       <c r="AI23" s="4">
-        <v>51.41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>51.47</v>
+      </c>
+      <c r="AJ23" s="4">
+        <v>39.59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C24" s="11">
         <v>5310</v>
@@ -3878,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U24" s="10"/>
       <c r="V24" s="10">
@@ -3893,7 +4021,9 @@
       <c r="Y24" s="14">
         <v>5.97</v>
       </c>
-      <c r="Z24" s="14"/>
+      <c r="Z24" s="14">
+        <v>99.78</v>
+      </c>
       <c r="AA24" s="14">
         <v>99.89</v>
       </c>
@@ -3921,13 +4051,16 @@
       <c r="AI24" s="14">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ24" s="14">
+        <v>65.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" s="1">
         <v>25342</v>
@@ -3981,10 +4114,10 @@
         <v>2</v>
       </c>
       <c r="T25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V25">
         <v>18</v>
@@ -3998,7 +4131,9 @@
       <c r="Y25" s="4">
         <v>11.76</v>
       </c>
-      <c r="Z25" s="4"/>
+      <c r="Z25" s="4">
+        <v>99.49</v>
+      </c>
       <c r="AA25" s="4">
         <v>99.57</v>
       </c>
@@ -4015,7 +4150,7 @@
         <v>12.8</v>
       </c>
       <c r="AF25" s="4">
-        <v>19.71</v>
+        <v>19.66</v>
       </c>
       <c r="AG25" s="4">
         <v>70.29</v>
@@ -4026,13 +4161,16 @@
       <c r="AI25" s="4">
         <v>3.45</v>
       </c>
-    </row>
-    <row r="26" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ25" s="4">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C26" s="11">
         <v>5576</v>
@@ -4086,10 +4224,10 @@
         <v>6</v>
       </c>
       <c r="T26" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V26" s="10">
         <v>12</v>
@@ -4103,7 +4241,9 @@
       <c r="Y26" s="14">
         <v>0</v>
       </c>
-      <c r="Z26" s="14"/>
+      <c r="Z26" s="14">
+        <v>99.81</v>
+      </c>
       <c r="AA26" s="14">
         <v>99.9</v>
       </c>
@@ -4131,13 +4271,16 @@
       <c r="AI26" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ26" s="14">
+        <v>77.28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C27" s="1">
         <v>9450</v>
@@ -4191,10 +4334,10 @@
         <v>3</v>
       </c>
       <c r="T27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="V27">
         <v>14</v>
@@ -4208,7 +4351,9 @@
       <c r="Y27" s="4">
         <v>7.9</v>
       </c>
-      <c r="Z27" s="4"/>
+      <c r="Z27" s="4">
+        <v>99.88</v>
+      </c>
       <c r="AA27" s="4">
         <v>99.91</v>
       </c>
@@ -4236,13 +4381,16 @@
       <c r="AI27" s="4">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="28" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ27" s="4">
+        <v>67.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="11">
         <v>1678</v>
@@ -4296,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U28" s="10"/>
       <c r="V28" s="10">
@@ -4311,7 +4459,9 @@
       <c r="Y28" s="14">
         <v>16.61</v>
       </c>
-      <c r="Z28" s="14"/>
+      <c r="Z28" s="14">
+        <v>100</v>
+      </c>
       <c r="AA28" s="14">
         <v>100</v>
       </c>
@@ -4339,13 +4489,16 @@
       <c r="AI28" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ28" s="14">
+        <v>70.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1">
         <v>7427</v>
@@ -4399,10 +4552,10 @@
         <v>1</v>
       </c>
       <c r="T29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V29">
         <v>27</v>
@@ -4416,7 +4569,9 @@
       <c r="Y29" s="4">
         <v>0.11</v>
       </c>
-      <c r="Z29" s="4"/>
+      <c r="Z29" s="4">
+        <v>100</v>
+      </c>
       <c r="AA29" s="4">
         <v>99.85</v>
       </c>
@@ -4444,13 +4599,16 @@
       <c r="AI29" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:35" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AJ29" s="4">
+        <v>70.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="11">
         <v>5672</v>
@@ -4504,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="T30" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V30" s="10">
         <v>19</v>
@@ -4521,7 +4679,9 @@
       <c r="Y30" s="14">
         <v>0</v>
       </c>
-      <c r="Z30" s="14"/>
+      <c r="Z30" s="14">
+        <v>99.96</v>
+      </c>
       <c r="AA30" s="14">
         <v>99.73</v>
       </c>
@@ -4549,13 +4709,16 @@
       <c r="AI30" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ30" s="14">
+        <v>81.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C31" s="1">
         <v>3200</v>
@@ -4609,10 +4772,10 @@
         <v>2</v>
       </c>
       <c r="T31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V31">
         <v>21</v>
@@ -4626,7 +4789,9 @@
       <c r="Y31" s="4">
         <v>0</v>
       </c>
-      <c r="Z31" s="4"/>
+      <c r="Z31" s="4">
+        <v>99.58</v>
+      </c>
       <c r="AA31" s="4">
         <v>99.83</v>
       </c>
@@ -4654,9 +4819,12 @@
       <c r="AI31" s="4">
         <v>0</v>
       </c>
+      <c r="AJ31" s="4">
+        <v>97.03</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI1"/>
+  <autoFilter ref="A1:AJ1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4664,7 +4832,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -4674,200 +4842,200 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B2" s="12">
         <v>-0.93</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" s="2">
         <v>-0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="12">
         <v>0.87</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B5" s="2">
         <v>0.87</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="12">
         <v>-0.64</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2">
         <v>0.63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" s="12">
         <v>0.57</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" s="2">
         <v>-0.56</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="12">
-        <v>-0.5</v>
+        <v>-0.54</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B11" s="2">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="12">
         <v>-0.48</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B13" s="2">
         <v>-0.44</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B14" s="12">
         <v>0.37</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2">
         <v>-0.3</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="12">
         <v>0.3</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2">
         <v>-0.2</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="12">
+        <v>-0.13</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="B18" s="12">
-        <v>0.13</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -4875,18 +5043,21 @@
         <v>102</v>
       </c>
       <c r="B19" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="12">
         <v>-0.13</v>
       </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
+      <c r="C20" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -4895,6 +5066,14 @@
       </c>
       <c r="C22" s="10" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -4920,39 +5099,39 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
@@ -4961,21 +5140,21 @@
         <v>0</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
         <v>117</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -4984,21 +5163,21 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>115</v>
       </c>
       <c r="E4" s="10">
         <v>0</v>
@@ -5007,21 +5186,21 @@
         <v>50</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
         <v>117</v>
-      </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5030,21 +5209,21 @@
         <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E6" s="10">
         <v>44</v>
@@ -5053,21 +5232,21 @@
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -5076,21 +5255,21 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E8" s="10">
         <v>11</v>
@@ -5099,21 +5278,21 @@
         <v>29</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -5122,21 +5301,21 @@
         <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E10" s="10">
         <v>33</v>
@@ -5145,21 +5324,21 @@
         <v>0</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -5168,21 +5347,21 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E12" s="10">
         <v>13</v>
@@ -5191,21 +5370,21 @@
         <v>1</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13">
         <v>14</v>
@@ -5214,21 +5393,21 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
@@ -5237,21 +5416,21 @@
         <v>0</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15">
         <v>25</v>
@@ -5260,21 +5439,21 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E16" s="10">
         <v>31</v>
@@ -5283,21 +5462,21 @@
         <v>0</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17">
         <v>36</v>
@@ -5306,21 +5485,21 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E18" s="10">
         <v>50</v>
@@ -5329,21 +5508,21 @@
         <v>0</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E19">
         <v>21</v>
@@ -5352,21 +5531,21 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E20" s="10">
         <v>27</v>
@@ -5375,21 +5554,21 @@
         <v>0</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E21">
         <v>24</v>
@@ -5398,21 +5577,21 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E22" s="10">
         <v>14</v>
@@ -5421,21 +5600,21 @@
         <v>0</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E23">
         <v>30</v>
@@ -5444,21 +5623,21 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E24" s="10">
         <v>18</v>
@@ -5467,21 +5646,21 @@
         <v>0</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E25">
         <v>13</v>
@@ -5490,21 +5669,21 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E26" s="10">
         <v>27</v>
@@ -5513,21 +5692,21 @@
         <v>0</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E27">
         <v>19</v>
@@ -5536,21 +5715,21 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="C28" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E28" s="10">
         <v>21</v>
@@ -5559,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -5583,27 +5762,27 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" s="11">
         <v>28</v>
@@ -5617,10 +5796,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1">
         <v>72</v>
@@ -5634,10 +5813,10 @@
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="11">
         <v>56</v>
@@ -5651,10 +5830,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="1">
         <v>144</v>
@@ -5668,10 +5847,10 @@
     </row>
     <row r="6" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" s="11">
         <v>80</v>
@@ -5685,10 +5864,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1">
         <v>72</v>
@@ -5702,10 +5881,10 @@
     </row>
     <row r="8" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C8" s="11">
         <v>80</v>
@@ -5719,10 +5898,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C9" s="1">
         <v>117</v>
@@ -5736,10 +5915,10 @@
     </row>
     <row r="10" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C10" s="11">
         <v>96</v>
@@ -5753,10 +5932,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C11" s="1">
         <v>41</v>
@@ -5770,10 +5949,10 @@
     </row>
     <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C12" s="11">
         <v>24</v>
@@ -5787,10 +5966,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1">
         <v>118</v>
@@ -5804,10 +5983,10 @@
     </row>
     <row r="14" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C14" s="11">
         <v>110</v>
@@ -5821,10 +6000,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C15" s="1">
         <v>31</v>
@@ -5855,172 +6034,172 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C2" s="10">
         <v>30</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C3">
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C4" s="10">
         <v>30</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C5">
         <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C6" s="10">
         <v>330</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C7">
         <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C8" s="10">
         <v>155</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C9">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C10" s="10">
         <v>14</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C11">
         <v>452</v>
       </c>
       <c r="D11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -6032,7 +6211,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="24" customWidth="1"/>
@@ -6041,786 +6220,786 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>205</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C21" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C25" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D25" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D27" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D29" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C31" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D31" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C33" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B41" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C41" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C43" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D43" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C45" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D45" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C49" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B51" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D51" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="52" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>292</v>
       </c>
       <c r="D53" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D55" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -6828,13 +7007,13 @@
         <v>172</v>
       </c>
       <c r="B57" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C57" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -6842,41 +7021,41 @@
         <v>172</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B59" t="s">
+        <v>201</v>
+      </c>
+      <c r="C59" t="s">
+        <v>201</v>
+      </c>
+      <c r="D59" t="s">
         <v>202</v>
-      </c>
-      <c r="C59" t="s">
-        <v>202</v>
-      </c>
-      <c r="D59" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="60" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>206</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -6884,13 +7063,13 @@
         <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="C61" t="s">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="D61" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -6898,27 +7077,27 @@
         <v>174</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>288</v>
+        <v>207</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>288</v>
+        <v>208</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B63" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C63" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D63" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="64" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -6926,13 +7105,13 @@
         <v>176</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -6940,335 +7119,335 @@
         <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C65" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D65" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B67" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C67" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="68" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B69" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C69" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D69" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B71" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C71" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D71" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="72" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B73" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C73" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="D73" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B75" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C75" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B77" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C77" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D77" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B79" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C79" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="80" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B81" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C81" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D81" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="82" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B83" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C83" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D83" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B85" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C85" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D85" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C87" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D87" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -7276,13 +7455,13 @@
         <v>184</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>309</v>
       </c>
       <c r="D89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -7290,251 +7469,279 @@
         <v>184</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B91" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="C91" t="s">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="D91" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="92" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B93" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C93" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D93" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="94" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B95" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C95" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B97" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C97" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D97" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>204</v>
+        <v>317</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>204</v>
+        <v>318</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B99" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D99" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="100" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>316</v>
+        <v>206</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B101" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="C101" t="s">
-        <v>288</v>
+        <v>321</v>
       </c>
       <c r="D101" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="102" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B103" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="C103" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="D103" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="104" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>318</v>
+        <v>267</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B105" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="C105" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="D105" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B107" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="D107" t="s">
-        <v>203</v>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>192</v>
+      </c>
+      <c r="B109" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" t="s">
+        <v>266</v>
+      </c>
+      <c r="D109" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>

--- a/data/Mapa_das_Desigualdades_Sao_Vicente.xlsx
+++ b/data/Mapa_das_Desigualdades_Sao_Vicente.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="337">
   <si>
     <t>Bairro</t>
   </si>
@@ -126,6 +126,39 @@
     <t>Sem rampa p/ cadeirante (%)</t>
   </si>
   <si>
+    <t>[SINT] IVS</t>
+  </si>
+  <si>
+    <t>[SINT] Desemprego (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Trabalho informal (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Pobreza (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Jovens fora da escola (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Mortalidade infantil (‰)</t>
+  </si>
+  <si>
+    <t>[SINT] Mães chefes baixa esc. (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Aglomeração domiciliar (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Deslocamento &gt; 1h (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Sem veículo (%)</t>
+  </si>
+  <si>
+    <t>[SINT] Criminalidade (/10mil)</t>
+  </si>
+  <si>
     <t>Área continental (rural)</t>
   </si>
   <si>
@@ -609,7 +642,7 @@
     <t>Gerado em</t>
   </si>
   <si>
-    <t>2026-07-21</t>
+    <t>2026-07-23</t>
   </si>
   <si>
     <t>Campo (GeoJSON)</t>
@@ -1000,9 +1033,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1052,12 +1086,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1073,12 +1108,16 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1422,7 +1461,7 @@
   <sheetPr>
     <tabColor rgb="FF007A4A"/>
   </sheetPr>
-  <dimension ref="A1:AJ31"/>
+  <dimension ref="A1:AU31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1458,204 +1497,279 @@
     <col min="34" max="34" width="11" style="4" customWidth="1"/>
     <col min="35" max="35" width="12" style="4" customWidth="1"/>
     <col min="36" max="36" width="14" style="4" customWidth="1"/>
+    <col min="37" max="37" width="10" style="5" customWidth="1"/>
+    <col min="38" max="38" width="13" style="4" customWidth="1"/>
+    <col min="39" max="39" width="14" style="4" customWidth="1"/>
+    <col min="40" max="40" width="12" style="4" customWidth="1"/>
+    <col min="41" max="42" width="15" style="4" customWidth="1"/>
+    <col min="43" max="44" width="16" style="4" customWidth="1"/>
+    <col min="45" max="45" width="15" style="4" customWidth="1"/>
+    <col min="46" max="46" width="13" style="4" customWidth="1"/>
+    <col min="47" max="47" width="15" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:36" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" ht="34" customHeight="1" spans="1:47" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Y1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="Z1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AB1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AC1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AD1" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AE1" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AF1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="9" t="s">
+      <c r="AG1" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="9" t="s">
+      <c r="AH1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AI1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="9" t="s">
+      <c r="AJ1" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="AK1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="AL1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="11">
+      <c r="AM1" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="13">
         <v>555</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="14">
         <v>84.9162</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="13">
         <v>7</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="15">
         <v>1565</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="14">
         <v>1.29</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="16">
         <v>0.06</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>10</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="12">
         <v>1</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="14">
         <v>18.02</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="13">
         <v>4172</v>
       </c>
-      <c r="M2" s="10">
-        <v>0</v>
-      </c>
-      <c r="N2" s="10">
-        <v>0</v>
-      </c>
-      <c r="O2" s="11">
-        <v>0</v>
-      </c>
-      <c r="P2" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="14">
+      <c r="M2" s="12">
+        <v>0</v>
+      </c>
+      <c r="N2" s="12">
+        <v>0</v>
+      </c>
+      <c r="O2" s="13">
+        <v>0</v>
+      </c>
+      <c r="P2" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="16">
         <v>87.54</v>
       </c>
-      <c r="R2" s="14">
+      <c r="R2" s="16">
         <v>133943.09</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="12">
         <v>2</v>
       </c>
-      <c r="T2" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10">
-        <v>0</v>
-      </c>
-      <c r="W2" s="11"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="14"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="14"/>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="14"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="T2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12">
+        <v>0</v>
+      </c>
+      <c r="W2" s="13"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="16"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="16"/>
+      <c r="AD2" s="16"/>
+      <c r="AE2" s="16"/>
+      <c r="AF2" s="16"/>
+      <c r="AG2" s="16"/>
+      <c r="AH2" s="16"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="16"/>
+      <c r="AK2" s="18">
+        <v>0.953</v>
+      </c>
+      <c r="AL2" s="16">
+        <v>21.5</v>
+      </c>
+      <c r="AM2" s="16">
+        <v>58.9</v>
+      </c>
+      <c r="AN2" s="16">
+        <v>53.4</v>
+      </c>
+      <c r="AO2" s="16">
+        <v>11.3</v>
+      </c>
+      <c r="AP2" s="16">
+        <v>30.2</v>
+      </c>
+      <c r="AQ2" s="16">
+        <v>33.4</v>
+      </c>
+      <c r="AR2" s="16">
+        <v>33.4</v>
+      </c>
+      <c r="AS2" s="16">
+        <v>51.2</v>
+      </c>
+      <c r="AT2" s="16">
+        <v>64.9</v>
+      </c>
+      <c r="AU2" s="16">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1">
         <v>7536</v>
@@ -1709,10 +1823,10 @@
         <v>4</v>
       </c>
       <c r="T3" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="V3">
         <v>19</v>
@@ -1759,123 +1873,189 @@
       <c r="AJ3" s="4">
         <v>79.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="11">
+      <c r="AK3" s="5">
+        <v>0.601</v>
+      </c>
+      <c r="AL3" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>46.4</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>38.8</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP3" s="4">
+        <v>20.5</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>22.5</v>
+      </c>
+      <c r="AR3" s="4">
+        <v>23.1</v>
+      </c>
+      <c r="AS3" s="4">
+        <v>32.2</v>
+      </c>
+      <c r="AT3" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="AU3" s="4">
+        <v>52.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="13">
         <v>9992</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="14">
         <v>0.3229</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="13">
         <v>31019</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="15">
         <v>5234</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="14">
         <v>4.32</v>
       </c>
-      <c r="H4" s="14">
-        <v>0</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
+      <c r="H4" s="16">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
         <v>4</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="14">
         <v>4</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="13">
         <v>247</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="12">
         <v>4</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="12">
         <v>10</v>
       </c>
-      <c r="O4" s="11">
+      <c r="O4" s="13">
         <v>779</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="16">
         <v>77.96</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="16">
         <v>0.5</v>
       </c>
-      <c r="R4" s="14">
+      <c r="R4" s="16">
         <v>0.16</v>
       </c>
-      <c r="S4" s="10">
+      <c r="S4" s="12">
         <v>1</v>
       </c>
-      <c r="T4" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="V4" s="10">
-        <v>0</v>
-      </c>
-      <c r="W4" s="11">
+      <c r="T4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="V4" s="12">
+        <v>0</v>
+      </c>
+      <c r="W4" s="13">
         <v>4822</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="16">
         <v>99.94</v>
       </c>
-      <c r="Y4" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="14">
+      <c r="Y4" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="16">
         <v>100</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="16">
         <v>99.92</v>
       </c>
-      <c r="AB4" s="12">
+      <c r="AB4" s="14">
         <v>99.72</v>
       </c>
-      <c r="AC4" s="14">
+      <c r="AC4" s="16">
         <v>25.86</v>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="16">
         <v>6.29</v>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="16">
         <v>29.53</v>
       </c>
-      <c r="AF4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="14">
+      <c r="AF4" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="16">
         <v>3.3</v>
       </c>
-      <c r="AH4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="14">
+      <c r="AH4" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="16">
         <v>72.56</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK4" s="18">
+        <v>0.018</v>
+      </c>
+      <c r="AL4" s="16">
+        <v>4</v>
+      </c>
+      <c r="AM4" s="16">
+        <v>18.5</v>
+      </c>
+      <c r="AN4" s="16">
+        <v>4.9</v>
+      </c>
+      <c r="AO4" s="16">
+        <v>0.8</v>
+      </c>
+      <c r="AP4" s="16">
+        <v>10.3</v>
+      </c>
+      <c r="AQ4" s="16">
+        <v>3.6</v>
+      </c>
+      <c r="AR4" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="AS4" s="16">
+        <v>8.1</v>
+      </c>
+      <c r="AT4" s="16">
+        <v>17.7</v>
+      </c>
+      <c r="AU4" s="16">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1">
         <v>14903</v>
@@ -1929,10 +2109,10 @@
         <v>7</v>
       </c>
       <c r="T5" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U5" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="V5">
         <v>44</v>
@@ -1979,123 +2159,189 @@
       <c r="AJ5" s="4">
         <v>78.16</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="AK5" s="5">
+        <v>0.649</v>
+      </c>
+      <c r="AL5" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="AM5" s="4">
+        <v>47.9</v>
+      </c>
+      <c r="AN5" s="4">
+        <v>37.1</v>
+      </c>
+      <c r="AO5" s="4">
+        <v>8.7</v>
+      </c>
+      <c r="AP5" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="AQ5" s="4">
+        <v>24</v>
+      </c>
+      <c r="AR5" s="4">
+        <v>25.9</v>
+      </c>
+      <c r="AS5" s="4">
+        <v>38.6</v>
+      </c>
+      <c r="AT5" s="4">
+        <v>46.5</v>
+      </c>
+      <c r="AU5" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="13">
         <v>8870</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <v>0.7828</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="13">
         <v>11357</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <v>4024</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="14">
         <v>3.32</v>
       </c>
-      <c r="H6" s="14">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
+      <c r="H6" s="16">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
         <v>13</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="14">
         <v>14.66</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="13">
         <v>33</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="12">
         <v>25</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="12">
         <v>14</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="13">
         <v>1069</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="16">
         <v>120.52</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="16">
         <v>1.92</v>
       </c>
-      <c r="R6" s="14">
+      <c r="R6" s="16">
         <v>1.69</v>
       </c>
-      <c r="S6" s="10">
+      <c r="S6" s="12">
         <v>6</v>
       </c>
-      <c r="T6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" s="10">
+      <c r="T6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="V6" s="12">
         <v>16</v>
       </c>
-      <c r="W6" s="11">
+      <c r="W6" s="13">
         <v>4185</v>
       </c>
-      <c r="X6" s="14">
+      <c r="X6" s="16">
         <v>99.88</v>
       </c>
-      <c r="Y6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="14">
+      <c r="Y6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="16">
         <v>99.95</v>
       </c>
-      <c r="AA6" s="14">
+      <c r="AA6" s="16">
         <v>99.76</v>
       </c>
-      <c r="AB6" s="12">
+      <c r="AB6" s="14">
         <v>99.16</v>
       </c>
-      <c r="AC6" s="14">
+      <c r="AC6" s="16">
         <v>34.61</v>
       </c>
-      <c r="AD6" s="14">
+      <c r="AD6" s="16">
         <v>6.39</v>
       </c>
-      <c r="AE6" s="14">
+      <c r="AE6" s="16">
         <v>28.34</v>
       </c>
-      <c r="AF6" s="14">
+      <c r="AF6" s="16">
         <v>0.1</v>
       </c>
-      <c r="AG6" s="14">
+      <c r="AG6" s="16">
         <v>52.31</v>
       </c>
-      <c r="AH6" s="14">
+      <c r="AH6" s="16">
         <v>28.6</v>
       </c>
-      <c r="AI6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="14">
+      <c r="AI6" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="16">
         <v>23.87</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK6" s="18">
+        <v>0.295</v>
+      </c>
+      <c r="AL6" s="16">
+        <v>9.2</v>
+      </c>
+      <c r="AM6" s="16">
+        <v>29.6</v>
+      </c>
+      <c r="AN6" s="16">
+        <v>21.2</v>
+      </c>
+      <c r="AO6" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="AP6" s="16">
+        <v>16.3</v>
+      </c>
+      <c r="AQ6" s="16">
+        <v>14.5</v>
+      </c>
+      <c r="AR6" s="16">
+        <v>10.8</v>
+      </c>
+      <c r="AS6" s="16">
+        <v>24.7</v>
+      </c>
+      <c r="AT6" s="16">
+        <v>31.7</v>
+      </c>
+      <c r="AU6" s="16">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1">
         <v>31596</v>
@@ -2149,10 +2395,10 @@
         <v>13</v>
       </c>
       <c r="T7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="V7">
         <v>58</v>
@@ -2199,121 +2445,187 @@
       <c r="AJ7" s="4">
         <v>56.59</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="AK7" s="5">
+        <v>0.667</v>
+      </c>
+      <c r="AL7" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="AM7" s="4">
+        <v>42.9</v>
+      </c>
+      <c r="AN7" s="4">
+        <v>38.4</v>
+      </c>
+      <c r="AO7" s="4">
+        <v>8.2</v>
+      </c>
+      <c r="AP7" s="4">
+        <v>25.9</v>
+      </c>
+      <c r="AQ7" s="4">
+        <v>25.4</v>
+      </c>
+      <c r="AR7" s="4">
+        <v>25.3</v>
+      </c>
+      <c r="AS7" s="4">
+        <v>41.7</v>
+      </c>
+      <c r="AT7" s="4">
+        <v>47.5</v>
+      </c>
+      <c r="AU7" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="13">
         <v>8644</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <v>0.742</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="13">
         <v>11676</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <v>2280</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="14">
         <v>1.88</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="16">
         <v>8.28</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="12">
         <v>4</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="12">
         <v>2</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="14">
         <v>2.31</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="13">
         <v>391</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="12">
         <v>15</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="12">
         <v>8</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="13">
         <v>606</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="16">
         <v>70.11</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="16">
         <v>1.19</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="16">
         <v>1.03</v>
       </c>
-      <c r="S8" s="10">
+      <c r="S8" s="12">
         <v>12</v>
       </c>
-      <c r="T8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10">
-        <v>0</v>
-      </c>
-      <c r="W8" s="11">
+      <c r="T8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
+      <c r="W8" s="13">
         <v>3167</v>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="16">
         <v>96.84</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="16">
         <v>2.49</v>
       </c>
-      <c r="Z8" s="14">
+      <c r="Z8" s="16">
         <v>99.78</v>
       </c>
-      <c r="AA8" s="14">
+      <c r="AA8" s="16">
         <v>99.87</v>
       </c>
-      <c r="AB8" s="12">
+      <c r="AB8" s="14">
         <v>97.54</v>
       </c>
-      <c r="AC8" s="14">
+      <c r="AC8" s="16">
         <v>50.97</v>
       </c>
-      <c r="AD8" s="14">
+      <c r="AD8" s="16">
         <v>11.38</v>
       </c>
-      <c r="AE8" s="14">
+      <c r="AE8" s="16">
         <v>17.87</v>
       </c>
-      <c r="AF8" s="14">
+      <c r="AF8" s="16">
         <v>4.8</v>
       </c>
-      <c r="AG8" s="14">
+      <c r="AG8" s="16">
         <v>40.29</v>
       </c>
-      <c r="AH8" s="14">
+      <c r="AH8" s="16">
         <v>9.47</v>
       </c>
-      <c r="AI8" s="14">
+      <c r="AI8" s="16">
         <v>2.37</v>
       </c>
-      <c r="AJ8" s="14">
+      <c r="AJ8" s="16">
         <v>84.24</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK8" s="18">
+        <v>0.775</v>
+      </c>
+      <c r="AL8" s="16">
+        <v>18</v>
+      </c>
+      <c r="AM8" s="16">
+        <v>47.7</v>
+      </c>
+      <c r="AN8" s="16">
+        <v>46.5</v>
+      </c>
+      <c r="AO8" s="16">
+        <v>11.4</v>
+      </c>
+      <c r="AP8" s="16">
+        <v>24.3</v>
+      </c>
+      <c r="AQ8" s="16">
+        <v>26.8</v>
+      </c>
+      <c r="AR8" s="16">
+        <v>26.1</v>
+      </c>
+      <c r="AS8" s="16">
+        <v>45.9</v>
+      </c>
+      <c r="AT8" s="16">
+        <v>55.3</v>
+      </c>
+      <c r="AU8" s="16">
+        <v>69.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
       </c>
       <c r="C9" s="1">
         <v>11360</v>
@@ -2367,10 +2679,10 @@
         <v>4</v>
       </c>
       <c r="T9" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U9" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="V9">
         <v>16</v>
@@ -2417,123 +2729,189 @@
       <c r="AJ9" s="4">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="10" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="AK9" s="5">
+        <v>0.186</v>
+      </c>
+      <c r="AL9" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="AM9" s="4">
+        <v>27.7</v>
+      </c>
+      <c r="AN9" s="4">
+        <v>16</v>
+      </c>
+      <c r="AO9" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="AP9" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="AR9" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="AS9" s="4">
+        <v>17</v>
+      </c>
+      <c r="AT9" s="4">
+        <v>28.6</v>
+      </c>
+      <c r="AU9" s="4">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="13">
+        <v>11685</v>
+      </c>
+      <c r="D10" s="14">
+        <v>7.7833</v>
+      </c>
+      <c r="E10" s="13">
+        <v>4724</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2192</v>
+      </c>
+      <c r="G10" s="14">
+        <v>1.81</v>
+      </c>
+      <c r="H10" s="16">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12">
+        <v>4</v>
+      </c>
+      <c r="K10" s="14">
+        <v>3.42</v>
+      </c>
+      <c r="L10" s="13">
+        <v>990</v>
+      </c>
+      <c r="M10" s="12">
+        <v>41</v>
+      </c>
+      <c r="N10" s="12">
+        <v>3</v>
+      </c>
+      <c r="O10" s="13">
+        <v>324</v>
+      </c>
+      <c r="P10" s="16">
+        <v>27.73</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>71.55</v>
+      </c>
+      <c r="R10" s="16">
+        <v>476.6</v>
+      </c>
+      <c r="S10" s="12">
+        <v>29</v>
+      </c>
+      <c r="T10" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="11">
-        <v>11685</v>
-      </c>
-      <c r="D10" s="12">
-        <v>7.7833</v>
-      </c>
-      <c r="E10" s="11">
-        <v>4724</v>
-      </c>
-      <c r="F10" s="13">
-        <v>2192</v>
-      </c>
-      <c r="G10" s="12">
-        <v>1.81</v>
-      </c>
-      <c r="H10" s="14">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10">
-        <v>1</v>
-      </c>
-      <c r="J10" s="10">
-        <v>4</v>
-      </c>
-      <c r="K10" s="12">
-        <v>3.42</v>
-      </c>
-      <c r="L10" s="11">
-        <v>990</v>
-      </c>
-      <c r="M10" s="10">
-        <v>41</v>
-      </c>
-      <c r="N10" s="10">
-        <v>3</v>
-      </c>
-      <c r="O10" s="11">
-        <v>324</v>
-      </c>
-      <c r="P10" s="14">
-        <v>27.73</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>71.55</v>
-      </c>
-      <c r="R10" s="14">
-        <v>476.6</v>
-      </c>
-      <c r="S10" s="10">
-        <v>29</v>
-      </c>
-      <c r="T10" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" s="10">
+      <c r="U10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" s="12">
         <v>33</v>
       </c>
-      <c r="W10" s="11">
+      <c r="W10" s="13">
         <v>3973</v>
       </c>
-      <c r="X10" s="14">
+      <c r="X10" s="16">
         <v>99.8</v>
       </c>
-      <c r="Y10" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="14">
+      <c r="Y10" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="16">
         <v>99.97</v>
       </c>
-      <c r="AA10" s="14">
+      <c r="AA10" s="16">
         <v>100</v>
       </c>
-      <c r="AB10" s="12">
+      <c r="AB10" s="14">
         <v>96.79</v>
       </c>
-      <c r="AC10" s="14">
+      <c r="AC10" s="16">
         <v>59.78</v>
       </c>
-      <c r="AD10" s="14">
+      <c r="AD10" s="16">
         <v>12.33</v>
       </c>
-      <c r="AE10" s="14">
+      <c r="AE10" s="16">
         <v>20.42</v>
       </c>
-      <c r="AF10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="14">
+      <c r="AF10" s="16">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="16">
         <v>45.94</v>
       </c>
-      <c r="AH10" s="14">
+      <c r="AH10" s="16">
         <v>74.35</v>
       </c>
-      <c r="AI10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="14">
+      <c r="AI10" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="16">
         <v>86.36</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK10" s="18">
+        <v>0.795</v>
+      </c>
+      <c r="AL10" s="16">
+        <v>19.5</v>
+      </c>
+      <c r="AM10" s="16">
+        <v>50.8</v>
+      </c>
+      <c r="AN10" s="16">
+        <v>49.6</v>
+      </c>
+      <c r="AO10" s="16">
+        <v>10.1</v>
+      </c>
+      <c r="AP10" s="16">
+        <v>24.5</v>
+      </c>
+      <c r="AQ10" s="16">
+        <v>27.2</v>
+      </c>
+      <c r="AR10" s="16">
+        <v>26.9</v>
+      </c>
+      <c r="AS10" s="16">
+        <v>45.8</v>
+      </c>
+      <c r="AT10" s="16">
+        <v>56.7</v>
+      </c>
+      <c r="AU10" s="16">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1">
         <v>8792</v>
@@ -2587,10 +2965,10 @@
         <v>7</v>
       </c>
       <c r="T11" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2637,123 +3015,189 @@
       <c r="AJ11" s="4">
         <v>57.48</v>
       </c>
-    </row>
-    <row r="12" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="AK11" s="5">
+        <v>0.153</v>
+      </c>
+      <c r="AL11" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="AM11" s="4">
+        <v>25.9</v>
+      </c>
+      <c r="AN11" s="4">
+        <v>14.1</v>
+      </c>
+      <c r="AO11" s="4">
+        <v>2</v>
+      </c>
+      <c r="AP11" s="4">
+        <v>11.3</v>
+      </c>
+      <c r="AQ11" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="AR11" s="4">
+        <v>8</v>
+      </c>
+      <c r="AS11" s="4">
+        <v>14.5</v>
+      </c>
+      <c r="AT11" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="AU11" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="13">
         <v>5694</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="14">
         <v>3.7094</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="13">
         <v>1539</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <v>2612</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="14">
         <v>2.16</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="16">
         <v>0.26</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="12">
         <v>1</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="12">
         <v>1</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="14">
         <v>1.76</v>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="13">
         <v>810</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="12">
         <v>10</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="12">
         <v>1</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="13">
         <v>31</v>
       </c>
-      <c r="P12" s="14">
+      <c r="P12" s="16">
         <v>5.44</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="16">
         <v>73.13</v>
       </c>
-      <c r="R12" s="14">
+      <c r="R12" s="16">
         <v>476.41</v>
       </c>
-      <c r="S12" s="10">
+      <c r="S12" s="12">
         <v>5</v>
       </c>
-      <c r="T12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V12" s="10">
+      <c r="T12" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="12">
         <v>14</v>
       </c>
-      <c r="W12" s="11">
+      <c r="W12" s="13">
         <v>2146</v>
       </c>
-      <c r="X12" s="14">
+      <c r="X12" s="16">
         <v>99.07</v>
       </c>
-      <c r="Y12" s="14">
+      <c r="Y12" s="16">
         <v>0.56</v>
       </c>
-      <c r="Z12" s="14">
+      <c r="Z12" s="16">
         <v>99.49</v>
       </c>
-      <c r="AA12" s="14">
+      <c r="AA12" s="16">
         <v>99.95</v>
       </c>
-      <c r="AB12" s="12">
+      <c r="AB12" s="14">
         <v>97.52</v>
       </c>
-      <c r="AC12" s="14">
+      <c r="AC12" s="16">
         <v>45.73</v>
       </c>
-      <c r="AD12" s="14">
+      <c r="AD12" s="16">
         <v>11.45</v>
       </c>
-      <c r="AE12" s="14">
+      <c r="AE12" s="16">
         <v>17.6</v>
       </c>
-      <c r="AF12" s="14">
+      <c r="AF12" s="16">
         <v>0.89</v>
       </c>
-      <c r="AG12" s="14">
+      <c r="AG12" s="16">
         <v>9.56</v>
       </c>
-      <c r="AH12" s="14">
+      <c r="AH12" s="16">
         <v>0.47</v>
       </c>
-      <c r="AI12" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="14">
+      <c r="AI12" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="16">
         <v>11.06</v>
       </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK12" s="18">
+        <v>0.696</v>
+      </c>
+      <c r="AL12" s="16">
+        <v>18.3</v>
+      </c>
+      <c r="AM12" s="16">
+        <v>46.9</v>
+      </c>
+      <c r="AN12" s="16">
+        <v>42.8</v>
+      </c>
+      <c r="AO12" s="16">
+        <v>9.6</v>
+      </c>
+      <c r="AP12" s="16">
+        <v>22.3</v>
+      </c>
+      <c r="AQ12" s="16">
+        <v>23.2</v>
+      </c>
+      <c r="AR12" s="16">
+        <v>25.2</v>
+      </c>
+      <c r="AS12" s="16">
+        <v>37.6</v>
+      </c>
+      <c r="AT12" s="16">
+        <v>53.9</v>
+      </c>
+      <c r="AU12" s="16">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1">
         <v>3454</v>
@@ -2807,10 +3251,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="V13">
         <v>13</v>
@@ -2857,123 +3301,189 @@
       <c r="AJ13" s="4">
         <v>70.23</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="AK13" s="5">
+        <v>0.604</v>
+      </c>
+      <c r="AL13" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="AM13" s="4">
+        <v>43.8</v>
+      </c>
+      <c r="AN13" s="4">
+        <v>35.7</v>
+      </c>
+      <c r="AO13" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="AP13" s="4">
+        <v>22</v>
+      </c>
+      <c r="AQ13" s="4">
+        <v>21.9</v>
+      </c>
+      <c r="AR13" s="4">
+        <v>22.5</v>
+      </c>
+      <c r="AS13" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="AT13" s="4">
+        <v>48.2</v>
+      </c>
+      <c r="AU13" s="4">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="13">
+        <v>3367</v>
+      </c>
+      <c r="D14" s="14">
+        <v>0.3526</v>
+      </c>
+      <c r="E14" s="13">
+        <v>9570</v>
+      </c>
+      <c r="F14" s="15">
+        <v>3721</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3.07</v>
+      </c>
+      <c r="H14" s="16">
+        <v>11.62</v>
+      </c>
+      <c r="I14" s="12">
+        <v>2</v>
+      </c>
+      <c r="J14" s="12">
+        <v>1</v>
+      </c>
+      <c r="K14" s="14">
+        <v>2.97</v>
+      </c>
+      <c r="L14" s="13">
+        <v>292</v>
+      </c>
+      <c r="M14" s="12">
+        <v>3</v>
+      </c>
+      <c r="N14" s="12">
+        <v>3</v>
+      </c>
+      <c r="O14" s="13">
+        <v>121</v>
+      </c>
+      <c r="P14" s="16">
+        <v>35.94</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>2.74</v>
+      </c>
+      <c r="R14" s="16">
+        <v>2.87</v>
+      </c>
+      <c r="S14" s="12">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="11">
-        <v>3367</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0.3526</v>
-      </c>
-      <c r="E14" s="11">
-        <v>9570</v>
-      </c>
-      <c r="F14" s="13">
-        <v>3721</v>
-      </c>
-      <c r="G14" s="12">
-        <v>3.07</v>
-      </c>
-      <c r="H14" s="14">
-        <v>11.62</v>
-      </c>
-      <c r="I14" s="10">
-        <v>2</v>
-      </c>
-      <c r="J14" s="10">
-        <v>1</v>
-      </c>
-      <c r="K14" s="12">
-        <v>2.97</v>
-      </c>
-      <c r="L14" s="11">
-        <v>292</v>
-      </c>
-      <c r="M14" s="10">
-        <v>3</v>
-      </c>
-      <c r="N14" s="10">
-        <v>3</v>
-      </c>
-      <c r="O14" s="11">
-        <v>121</v>
-      </c>
-      <c r="P14" s="14">
-        <v>35.94</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>2.74</v>
-      </c>
-      <c r="R14" s="14">
-        <v>2.87</v>
-      </c>
-      <c r="S14" s="10">
-        <v>0</v>
-      </c>
-      <c r="T14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V14" s="10">
+      <c r="V14" s="12">
         <v>13</v>
       </c>
-      <c r="W14" s="11">
+      <c r="W14" s="13">
         <v>1261</v>
       </c>
-      <c r="X14" s="14">
+      <c r="X14" s="16">
         <v>98.57</v>
       </c>
-      <c r="Y14" s="14">
+      <c r="Y14" s="16">
         <v>0.87</v>
       </c>
-      <c r="Z14" s="14">
+      <c r="Z14" s="16">
         <v>100</v>
       </c>
-      <c r="AA14" s="14">
+      <c r="AA14" s="16">
         <v>99.76</v>
       </c>
-      <c r="AB14" s="12">
+      <c r="AB14" s="14">
         <v>98.55</v>
       </c>
-      <c r="AC14" s="14">
+      <c r="AC14" s="16">
         <v>36.91</v>
       </c>
-      <c r="AD14" s="14">
+      <c r="AD14" s="16">
         <v>8.41</v>
       </c>
-      <c r="AE14" s="14">
+      <c r="AE14" s="16">
         <v>21.86</v>
       </c>
-      <c r="AF14" s="14">
+      <c r="AF14" s="16">
         <v>10.86</v>
       </c>
-      <c r="AG14" s="14">
+      <c r="AG14" s="16">
         <v>30.29</v>
       </c>
-      <c r="AH14" s="14">
+      <c r="AH14" s="16">
         <v>18.16</v>
       </c>
-      <c r="AI14" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="14">
+      <c r="AI14" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="16">
         <v>87.71</v>
       </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK14" s="18">
+        <v>0.358</v>
+      </c>
+      <c r="AL14" s="16">
+        <v>8.3</v>
+      </c>
+      <c r="AM14" s="16">
+        <v>30</v>
+      </c>
+      <c r="AN14" s="16">
+        <v>20.2</v>
+      </c>
+      <c r="AO14" s="16">
+        <v>6.7</v>
+      </c>
+      <c r="AP14" s="16">
+        <v>19</v>
+      </c>
+      <c r="AQ14" s="16">
+        <v>15.6</v>
+      </c>
+      <c r="AR14" s="16">
+        <v>13.7</v>
+      </c>
+      <c r="AS14" s="16">
+        <v>27.2</v>
+      </c>
+      <c r="AT14" s="16">
+        <v>36.5</v>
+      </c>
+      <c r="AU14" s="16">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C15" s="1">
         <v>24906</v>
@@ -3026,8 +3536,8 @@
       <c r="S15">
         <v>3</v>
       </c>
-      <c r="T15" s="16" t="s">
-        <v>38</v>
+      <c r="T15" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3074,123 +3584,189 @@
       <c r="AJ15" s="4">
         <v>62.94</v>
       </c>
-    </row>
-    <row r="16" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="AK15" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="AL15" s="4">
+        <v>20.9</v>
+      </c>
+      <c r="AM15" s="4">
+        <v>52.6</v>
+      </c>
+      <c r="AN15" s="4">
+        <v>53.5</v>
+      </c>
+      <c r="AO15" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="AP15" s="4">
+        <v>30.2</v>
+      </c>
+      <c r="AQ15" s="4">
+        <v>29.2</v>
+      </c>
+      <c r="AR15" s="4">
+        <v>31.9</v>
+      </c>
+      <c r="AS15" s="4">
+        <v>50</v>
+      </c>
+      <c r="AT15" s="4">
+        <v>59.5</v>
+      </c>
+      <c r="AU15" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="13">
+        <v>20472</v>
+      </c>
+      <c r="D16" s="14">
+        <v>6.3487</v>
+      </c>
+      <c r="E16" s="13">
+        <v>3349</v>
+      </c>
+      <c r="F16" s="15">
+        <v>3135</v>
+      </c>
+      <c r="G16" s="14">
+        <v>2.59</v>
+      </c>
+      <c r="H16" s="16">
+        <v>9.52</v>
+      </c>
+      <c r="I16" s="12">
+        <v>4</v>
+      </c>
+      <c r="J16" s="12">
+        <v>7</v>
+      </c>
+      <c r="K16" s="14">
+        <v>3.42</v>
+      </c>
+      <c r="L16" s="13">
+        <v>211</v>
+      </c>
+      <c r="M16" s="12">
+        <v>35</v>
+      </c>
+      <c r="N16" s="12">
+        <v>6</v>
+      </c>
+      <c r="O16" s="13">
+        <v>506</v>
+      </c>
+      <c r="P16" s="16">
+        <v>24.72</v>
+      </c>
+      <c r="Q16" s="16">
+        <v>14.83</v>
+      </c>
+      <c r="R16" s="16">
+        <v>46</v>
+      </c>
+      <c r="S16" s="12">
+        <v>2</v>
+      </c>
+      <c r="T16" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="V16" s="12">
+        <v>1</v>
+      </c>
+      <c r="W16" s="13">
+        <v>5772</v>
+      </c>
+      <c r="X16" s="16">
+        <v>98.89</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>0.12</v>
+      </c>
+      <c r="Z16" s="16">
+        <v>99.9</v>
+      </c>
+      <c r="AA16" s="16">
+        <v>99.57</v>
+      </c>
+      <c r="AB16" s="14">
+        <v>95.25</v>
+      </c>
+      <c r="AC16" s="16">
+        <v>63.56</v>
+      </c>
+      <c r="AD16" s="16">
+        <v>11.61</v>
+      </c>
+      <c r="AE16" s="16">
+        <v>9.84</v>
+      </c>
+      <c r="AF16" s="16">
+        <v>5.06</v>
+      </c>
+      <c r="AG16" s="16">
+        <v>30.2</v>
+      </c>
+      <c r="AH16" s="16">
+        <v>14.52</v>
+      </c>
+      <c r="AI16" s="16">
+        <v>9.67</v>
+      </c>
+      <c r="AJ16" s="16">
+        <v>65.54</v>
+      </c>
+      <c r="AK16" s="18">
+        <v>0.512</v>
+      </c>
+      <c r="AL16" s="16">
+        <v>12.6</v>
+      </c>
+      <c r="AM16" s="16">
         <v>40</v>
       </c>
-      <c r="C16" s="11">
-        <v>20472</v>
-      </c>
-      <c r="D16" s="12">
-        <v>6.3487</v>
-      </c>
-      <c r="E16" s="11">
-        <v>3349</v>
-      </c>
-      <c r="F16" s="13">
-        <v>3135</v>
-      </c>
-      <c r="G16" s="12">
-        <v>2.59</v>
-      </c>
-      <c r="H16" s="14">
-        <v>9.52</v>
-      </c>
-      <c r="I16" s="10">
-        <v>4</v>
-      </c>
-      <c r="J16" s="10">
-        <v>7</v>
-      </c>
-      <c r="K16" s="12">
-        <v>3.42</v>
-      </c>
-      <c r="L16" s="11">
-        <v>211</v>
-      </c>
-      <c r="M16" s="10">
-        <v>35</v>
-      </c>
-      <c r="N16" s="10">
-        <v>6</v>
-      </c>
-      <c r="O16" s="11">
-        <v>506</v>
-      </c>
-      <c r="P16" s="14">
-        <v>24.72</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>14.83</v>
-      </c>
-      <c r="R16" s="14">
-        <v>46</v>
-      </c>
-      <c r="S16" s="10">
-        <v>2</v>
-      </c>
-      <c r="T16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U16" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="V16" s="10">
-        <v>1</v>
-      </c>
-      <c r="W16" s="11">
-        <v>5772</v>
-      </c>
-      <c r="X16" s="14">
-        <v>98.89</v>
-      </c>
-      <c r="Y16" s="14">
-        <v>0.12</v>
-      </c>
-      <c r="Z16" s="14">
-        <v>99.9</v>
-      </c>
-      <c r="AA16" s="14">
-        <v>99.57</v>
-      </c>
-      <c r="AB16" s="12">
-        <v>95.25</v>
-      </c>
-      <c r="AC16" s="14">
-        <v>63.56</v>
-      </c>
-      <c r="AD16" s="14">
-        <v>11.61</v>
-      </c>
-      <c r="AE16" s="14">
-        <v>9.84</v>
-      </c>
-      <c r="AF16" s="14">
-        <v>5.06</v>
-      </c>
-      <c r="AG16" s="14">
-        <v>30.2</v>
-      </c>
-      <c r="AH16" s="14">
-        <v>14.52</v>
-      </c>
-      <c r="AI16" s="14">
-        <v>9.67</v>
-      </c>
-      <c r="AJ16" s="14">
-        <v>65.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AN16" s="16">
+        <v>30.1</v>
+      </c>
+      <c r="AO16" s="16">
+        <v>6.2</v>
+      </c>
+      <c r="AP16" s="16">
+        <v>21.8</v>
+      </c>
+      <c r="AQ16" s="16">
+        <v>21.5</v>
+      </c>
+      <c r="AR16" s="16">
+        <v>21.9</v>
+      </c>
+      <c r="AS16" s="16">
+        <v>28.9</v>
+      </c>
+      <c r="AT16" s="16">
+        <v>42.5</v>
+      </c>
+      <c r="AU16" s="16">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1">
         <v>28265</v>
@@ -3244,10 +3820,10 @@
         <v>18</v>
       </c>
       <c r="T17" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U17" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="V17">
         <v>27</v>
@@ -3294,121 +3870,187 @@
       <c r="AJ17" s="4">
         <v>75.35</v>
       </c>
-    </row>
-    <row r="18" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="AK17" s="5">
+        <v>0.863</v>
+      </c>
+      <c r="AL17" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="AM17" s="4">
+        <v>56</v>
+      </c>
+      <c r="AN17" s="4">
+        <v>49.4</v>
+      </c>
+      <c r="AO17" s="4">
+        <v>12.1</v>
+      </c>
+      <c r="AP17" s="4">
+        <v>29.7</v>
+      </c>
+      <c r="AQ17" s="4">
+        <v>29.9</v>
+      </c>
+      <c r="AR17" s="4">
+        <v>28.4</v>
+      </c>
+      <c r="AS17" s="4">
+        <v>46.1</v>
+      </c>
+      <c r="AT17" s="4">
+        <v>60</v>
+      </c>
+      <c r="AU17" s="4">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="13">
         <v>4075</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="14">
         <v>0.3663</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="13">
         <v>11149</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="15">
         <v>2064</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="14">
         <v>1.7</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="16">
         <v>22.6</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="12">
         <v>2</v>
       </c>
-      <c r="J18" s="10">
-        <v>0</v>
-      </c>
-      <c r="K18" s="12">
-        <v>0</v>
-      </c>
-      <c r="L18" s="11">
+      <c r="J18" s="12">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
         <v>507</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="12">
         <v>8</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="12">
         <v>1</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="13">
         <v>117</v>
       </c>
-      <c r="P18" s="14">
+      <c r="P18" s="16">
         <v>28.71</v>
       </c>
-      <c r="Q18" s="14">
+      <c r="Q18" s="16">
         <v>0.45</v>
       </c>
-      <c r="R18" s="14">
+      <c r="R18" s="16">
         <v>0.41</v>
       </c>
-      <c r="S18" s="10">
+      <c r="S18" s="12">
         <v>4</v>
       </c>
-      <c r="T18" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10">
-        <v>0</v>
-      </c>
-      <c r="W18" s="11">
+      <c r="T18" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="13">
         <v>1375</v>
       </c>
-      <c r="X18" s="14">
+      <c r="X18" s="16">
         <v>92</v>
       </c>
-      <c r="Y18" s="14">
+      <c r="Y18" s="16">
         <v>7.56</v>
       </c>
-      <c r="Z18" s="14">
+      <c r="Z18" s="16">
         <v>99.93</v>
       </c>
-      <c r="AA18" s="14">
+      <c r="AA18" s="16">
         <v>99.78</v>
       </c>
-      <c r="AB18" s="12">
+      <c r="AB18" s="14">
         <v>94.34</v>
       </c>
-      <c r="AC18" s="14">
+      <c r="AC18" s="16">
         <v>60.19</v>
       </c>
-      <c r="AD18" s="14">
+      <c r="AD18" s="16">
         <v>14.53</v>
       </c>
-      <c r="AE18" s="14">
+      <c r="AE18" s="16">
         <v>12.69</v>
       </c>
-      <c r="AF18" s="14">
+      <c r="AF18" s="16">
         <v>8.95</v>
       </c>
-      <c r="AG18" s="14">
+      <c r="AG18" s="16">
         <v>27.71</v>
       </c>
-      <c r="AH18" s="14">
+      <c r="AH18" s="16">
         <v>14.55</v>
       </c>
-      <c r="AI18" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="14">
+      <c r="AI18" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="16">
         <v>79.71</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK18" s="18">
+        <v>0.843</v>
+      </c>
+      <c r="AL18" s="16">
+        <v>17.7</v>
+      </c>
+      <c r="AM18" s="16">
+        <v>56.4</v>
+      </c>
+      <c r="AN18" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="AO18" s="16">
+        <v>11.1</v>
+      </c>
+      <c r="AP18" s="16">
+        <v>29.5</v>
+      </c>
+      <c r="AQ18" s="16">
+        <v>27.5</v>
+      </c>
+      <c r="AR18" s="16">
+        <v>28.5</v>
+      </c>
+      <c r="AS18" s="16">
+        <v>48</v>
+      </c>
+      <c r="AT18" s="16">
+        <v>56.1</v>
+      </c>
+      <c r="AU18" s="16">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1">
         <v>14351</v>
@@ -3462,10 +4104,10 @@
         <v>7</v>
       </c>
       <c r="T19" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U19" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="V19">
         <v>31</v>
@@ -3512,123 +4154,189 @@
       <c r="AJ19" s="4">
         <v>59.93</v>
       </c>
-    </row>
-    <row r="20" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="11">
+      <c r="AK19" s="5">
+        <v>0.649</v>
+      </c>
+      <c r="AL19" s="4">
+        <v>15.3</v>
+      </c>
+      <c r="AM19" s="4">
+        <v>43</v>
+      </c>
+      <c r="AN19" s="4">
+        <v>36.2</v>
+      </c>
+      <c r="AO19" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="AP19" s="4">
+        <v>26.1</v>
+      </c>
+      <c r="AQ19" s="4">
+        <v>23.4</v>
+      </c>
+      <c r="AR19" s="4">
+        <v>22.1</v>
+      </c>
+      <c r="AS19" s="4">
+        <v>36.6</v>
+      </c>
+      <c r="AT19" s="4">
+        <v>53.6</v>
+      </c>
+      <c r="AU19" s="4">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="13">
         <v>13171</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="14">
         <v>0.9688</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="13">
         <v>13626</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="15">
         <v>2338</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="14">
         <v>1.93</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="16">
         <v>5.86</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="12">
         <v>2</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="12">
         <v>1</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="14">
         <v>0.76</v>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="13">
         <v>189</v>
       </c>
-      <c r="M20" s="10">
+      <c r="M20" s="12">
         <v>21</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="12">
         <v>5</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="13">
         <v>389</v>
       </c>
-      <c r="P20" s="14">
+      <c r="P20" s="16">
         <v>29.53</v>
       </c>
-      <c r="Q20" s="14">
+      <c r="Q20" s="16">
         <v>0.47</v>
       </c>
-      <c r="R20" s="14">
+      <c r="R20" s="16">
         <v>0.35</v>
       </c>
-      <c r="S20" s="10">
+      <c r="S20" s="12">
         <v>9</v>
       </c>
-      <c r="T20" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U20" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V20" s="10">
+      <c r="T20" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U20" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="V20" s="12">
         <v>35</v>
       </c>
-      <c r="W20" s="11">
+      <c r="W20" s="13">
         <v>4458</v>
       </c>
-      <c r="X20" s="14">
+      <c r="X20" s="16">
         <v>93.41</v>
       </c>
-      <c r="Y20" s="14">
+      <c r="Y20" s="16">
         <v>6.48</v>
       </c>
-      <c r="Z20" s="14">
+      <c r="Z20" s="16">
         <v>99.98</v>
       </c>
-      <c r="AA20" s="14">
+      <c r="AA20" s="16">
         <v>99.98</v>
       </c>
-      <c r="AB20" s="12">
+      <c r="AB20" s="14">
         <v>97</v>
       </c>
-      <c r="AC20" s="14">
+      <c r="AC20" s="16">
         <v>62.1</v>
       </c>
-      <c r="AD20" s="14">
+      <c r="AD20" s="16">
         <v>13.52</v>
       </c>
-      <c r="AE20" s="14">
+      <c r="AE20" s="16">
         <v>13.21</v>
       </c>
-      <c r="AF20" s="14">
+      <c r="AF20" s="16">
         <v>3.39</v>
       </c>
-      <c r="AG20" s="14">
+      <c r="AG20" s="16">
         <v>14.22</v>
       </c>
-      <c r="AH20" s="14">
+      <c r="AH20" s="16">
         <v>15.55</v>
       </c>
-      <c r="AI20" s="14">
+      <c r="AI20" s="16">
         <v>0.74</v>
       </c>
-      <c r="AJ20" s="14">
+      <c r="AJ20" s="16">
         <v>58.7</v>
       </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK20" s="18">
+        <v>0.753</v>
+      </c>
+      <c r="AL20" s="16">
+        <v>17.4</v>
+      </c>
+      <c r="AM20" s="16">
+        <v>46.1</v>
+      </c>
+      <c r="AN20" s="16">
+        <v>41.7</v>
+      </c>
+      <c r="AO20" s="16">
+        <v>10.9</v>
+      </c>
+      <c r="AP20" s="16">
+        <v>26.6</v>
+      </c>
+      <c r="AQ20" s="16">
+        <v>23.8</v>
+      </c>
+      <c r="AR20" s="16">
+        <v>29.4</v>
+      </c>
+      <c r="AS20" s="16">
+        <v>45.2</v>
+      </c>
+      <c r="AT20" s="16">
+        <v>52.5</v>
+      </c>
+      <c r="AU20" s="16">
+        <v>73.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>11980</v>
@@ -3681,8 +4389,8 @@
       <c r="S21">
         <v>8</v>
       </c>
-      <c r="T21" s="16" t="s">
-        <v>38</v>
+      <c r="T21" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3729,123 +4437,189 @@
       <c r="AJ21" s="4">
         <v>86.04</v>
       </c>
-    </row>
-    <row r="22" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="11">
+      <c r="AK21" s="5">
+        <v>0.678</v>
+      </c>
+      <c r="AL21" s="4">
+        <v>17.7</v>
+      </c>
+      <c r="AM21" s="4">
+        <v>46.1</v>
+      </c>
+      <c r="AN21" s="4">
+        <v>37.8</v>
+      </c>
+      <c r="AO21" s="4">
+        <v>9.4</v>
+      </c>
+      <c r="AP21" s="4">
+        <v>24.8</v>
+      </c>
+      <c r="AQ21" s="4">
+        <v>24.3</v>
+      </c>
+      <c r="AR21" s="4">
+        <v>24.2</v>
+      </c>
+      <c r="AS21" s="4">
+        <v>36.9</v>
+      </c>
+      <c r="AT21" s="4">
+        <v>49.4</v>
+      </c>
+      <c r="AU21" s="4">
+        <v>61.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="13">
         <v>10374</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="14">
         <v>0.7704</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="13">
         <v>13496</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="15">
         <v>2798</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="14">
         <v>2.31</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="16">
         <v>2.98</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="12">
         <v>3</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <v>1</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="14">
         <v>0.96</v>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="13">
         <v>339</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="12">
         <v>12</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="12">
         <v>5</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="13">
         <v>432</v>
       </c>
-      <c r="P22" s="14">
+      <c r="P22" s="16">
         <v>41.64</v>
       </c>
-      <c r="Q22" s="14">
+      <c r="Q22" s="16">
         <v>0.8</v>
       </c>
-      <c r="R22" s="14">
+      <c r="R22" s="16">
         <v>0.6</v>
       </c>
-      <c r="S22" s="10">
+      <c r="S22" s="12">
         <v>3</v>
       </c>
-      <c r="T22" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U22" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="V22" s="10">
+      <c r="T22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U22" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="V22" s="12">
         <v>49</v>
       </c>
-      <c r="W22" s="11">
+      <c r="W22" s="13">
         <v>3729</v>
       </c>
-      <c r="X22" s="14">
+      <c r="X22" s="16">
         <v>99.44</v>
       </c>
-      <c r="Y22" s="14">
+      <c r="Y22" s="16">
         <v>0.13</v>
       </c>
-      <c r="Z22" s="14">
+      <c r="Z22" s="16">
         <v>99.97</v>
       </c>
-      <c r="AA22" s="14">
+      <c r="AA22" s="16">
         <v>99.87</v>
       </c>
-      <c r="AB22" s="12">
+      <c r="AB22" s="14">
         <v>97.68</v>
       </c>
-      <c r="AC22" s="14">
+      <c r="AC22" s="16">
         <v>48.03</v>
       </c>
-      <c r="AD22" s="14">
+      <c r="AD22" s="16">
         <v>11.41</v>
       </c>
-      <c r="AE22" s="14">
+      <c r="AE22" s="16">
         <v>17.88</v>
       </c>
-      <c r="AF22" s="14">
+      <c r="AF22" s="16">
         <v>1.07</v>
       </c>
-      <c r="AG22" s="14">
+      <c r="AG22" s="16">
         <v>41.6</v>
       </c>
-      <c r="AH22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="14">
+      <c r="AH22" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="16">
         <v>65.08</v>
       </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK22" s="18">
+        <v>0.577</v>
+      </c>
+      <c r="AL22" s="16">
+        <v>13.8</v>
+      </c>
+      <c r="AM22" s="16">
+        <v>40.6</v>
+      </c>
+      <c r="AN22" s="16">
+        <v>35.4</v>
+      </c>
+      <c r="AO22" s="16">
+        <v>7</v>
+      </c>
+      <c r="AP22" s="16">
+        <v>20.8</v>
+      </c>
+      <c r="AQ22" s="16">
+        <v>21.1</v>
+      </c>
+      <c r="AR22" s="16">
+        <v>25.3</v>
+      </c>
+      <c r="AS22" s="16">
+        <v>34.2</v>
+      </c>
+      <c r="AT22" s="16">
+        <v>49.4</v>
+      </c>
+      <c r="AU22" s="16">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1">
         <v>11148</v>
@@ -3898,8 +4672,8 @@
       <c r="S23">
         <v>2</v>
       </c>
-      <c r="T23" s="16" t="s">
-        <v>38</v>
+      <c r="T23" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3946,121 +4720,187 @@
       <c r="AJ23" s="4">
         <v>39.59</v>
       </c>
-    </row>
-    <row r="24" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="11">
+      <c r="AK23" s="5">
+        <v>0.909</v>
+      </c>
+      <c r="AL23" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="AM23" s="4">
+        <v>55.9</v>
+      </c>
+      <c r="AN23" s="4">
+        <v>57.4</v>
+      </c>
+      <c r="AO23" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="AP23" s="4">
+        <v>27.2</v>
+      </c>
+      <c r="AQ23" s="4">
+        <v>28.3</v>
+      </c>
+      <c r="AR23" s="4">
+        <v>32.7</v>
+      </c>
+      <c r="AS23" s="4">
+        <v>51.6</v>
+      </c>
+      <c r="AT23" s="4">
+        <v>58.4</v>
+      </c>
+      <c r="AU23" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="13">
         <v>5310</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="14">
         <v>0.5078</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="13">
         <v>10480</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="15">
         <v>2141</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="14">
         <v>1.77</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="16">
         <v>15.37</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="12">
         <v>3</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="12">
         <v>1</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="14">
         <v>1.88</v>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="13">
         <v>257</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="12">
         <v>9</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="12">
         <v>1</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="13">
         <v>117</v>
       </c>
-      <c r="P24" s="14">
+      <c r="P24" s="16">
         <v>22.03</v>
       </c>
-      <c r="Q24" s="14">
-        <v>0</v>
-      </c>
-      <c r="R24" s="14">
-        <v>0</v>
-      </c>
-      <c r="S24" s="10">
+      <c r="Q24" s="16">
+        <v>0</v>
+      </c>
+      <c r="R24" s="16">
+        <v>0</v>
+      </c>
+      <c r="S24" s="12">
         <v>1</v>
       </c>
-      <c r="T24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10">
-        <v>0</v>
-      </c>
-      <c r="W24" s="11">
+      <c r="T24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12">
+        <v>0</v>
+      </c>
+      <c r="W24" s="13">
         <v>1844</v>
       </c>
-      <c r="X24" s="14">
+      <c r="X24" s="16">
         <v>92.79</v>
       </c>
-      <c r="Y24" s="14">
+      <c r="Y24" s="16">
         <v>5.97</v>
       </c>
-      <c r="Z24" s="14">
+      <c r="Z24" s="16">
         <v>99.78</v>
       </c>
-      <c r="AA24" s="14">
+      <c r="AA24" s="16">
         <v>99.89</v>
       </c>
-      <c r="AB24" s="12">
+      <c r="AB24" s="14">
         <v>95.57</v>
       </c>
-      <c r="AC24" s="14">
+      <c r="AC24" s="16">
         <v>58.06</v>
       </c>
-      <c r="AD24" s="14">
+      <c r="AD24" s="16">
         <v>15.48</v>
       </c>
-      <c r="AE24" s="14">
+      <c r="AE24" s="16">
         <v>11.43</v>
       </c>
-      <c r="AF24" s="14">
+      <c r="AF24" s="16">
         <v>8.19</v>
       </c>
-      <c r="AG24" s="14">
+      <c r="AG24" s="16">
         <v>45.72</v>
       </c>
-      <c r="AH24" s="14">
+      <c r="AH24" s="16">
         <v>19.85</v>
       </c>
-      <c r="AI24" s="14">
+      <c r="AI24" s="16">
         <v>0.87</v>
       </c>
-      <c r="AJ24" s="14">
+      <c r="AJ24" s="16">
         <v>65.18</v>
       </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK24" s="18">
+        <v>0.764</v>
+      </c>
+      <c r="AL24" s="16">
+        <v>17.6</v>
+      </c>
+      <c r="AM24" s="16">
+        <v>49.9</v>
+      </c>
+      <c r="AN24" s="16">
+        <v>46.3</v>
+      </c>
+      <c r="AO24" s="16">
+        <v>11</v>
+      </c>
+      <c r="AP24" s="16">
+        <v>26.3</v>
+      </c>
+      <c r="AQ24" s="16">
+        <v>26.4</v>
+      </c>
+      <c r="AR24" s="16">
+        <v>25.8</v>
+      </c>
+      <c r="AS24" s="16">
+        <v>41</v>
+      </c>
+      <c r="AT24" s="16">
+        <v>54.2</v>
+      </c>
+      <c r="AU24" s="16">
+        <v>74.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C25" s="1">
         <v>25342</v>
@@ -4114,10 +4954,10 @@
         <v>2</v>
       </c>
       <c r="T25" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U25" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="V25">
         <v>18</v>
@@ -4164,123 +5004,189 @@
       <c r="AJ25" s="4">
         <v>77.8</v>
       </c>
-    </row>
-    <row r="26" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="11">
+      <c r="AK25" s="5">
+        <v>0.938</v>
+      </c>
+      <c r="AL25" s="4">
+        <v>21.5</v>
+      </c>
+      <c r="AM25" s="4">
+        <v>55.8</v>
+      </c>
+      <c r="AN25" s="4">
+        <v>56.9</v>
+      </c>
+      <c r="AO25" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="AP25" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="AQ25" s="4">
+        <v>28.5</v>
+      </c>
+      <c r="AR25" s="4">
+        <v>31</v>
+      </c>
+      <c r="AS25" s="4">
+        <v>51.7</v>
+      </c>
+      <c r="AT25" s="4">
+        <v>62.4</v>
+      </c>
+      <c r="AU25" s="4">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="13">
         <v>5576</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="14">
         <v>0.7211</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="13">
         <v>7750</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="15">
         <v>3562</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="14">
         <v>2.94</v>
       </c>
-      <c r="H26" s="14">
-        <v>0</v>
-      </c>
-      <c r="I26" s="10">
-        <v>0</v>
-      </c>
-      <c r="J26" s="10">
+      <c r="H26" s="16">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12">
         <v>1</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="14">
         <v>1.79</v>
       </c>
-      <c r="L26" s="11">
+      <c r="L26" s="13">
         <v>422</v>
       </c>
-      <c r="M26" s="10">
+      <c r="M26" s="12">
         <v>3</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="12">
         <v>7</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="13">
         <v>491</v>
       </c>
-      <c r="P26" s="14">
+      <c r="P26" s="16">
         <v>88.06</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="Q26" s="16">
         <v>3.9</v>
       </c>
-      <c r="R26" s="14">
+      <c r="R26" s="16">
         <v>5.05</v>
       </c>
-      <c r="S26" s="10">
+      <c r="S26" s="12">
         <v>6</v>
       </c>
-      <c r="T26" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="V26" s="10">
+      <c r="T26" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U26" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="V26" s="12">
         <v>12</v>
       </c>
-      <c r="W26" s="11">
+      <c r="W26" s="13">
         <v>2086</v>
       </c>
-      <c r="X26" s="14">
+      <c r="X26" s="16">
         <v>99.81</v>
       </c>
-      <c r="Y26" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="14">
+      <c r="Y26" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="16">
         <v>99.81</v>
       </c>
-      <c r="AA26" s="14">
+      <c r="AA26" s="16">
         <v>99.9</v>
       </c>
-      <c r="AB26" s="12">
+      <c r="AB26" s="14">
         <v>98.71</v>
       </c>
-      <c r="AC26" s="14">
+      <c r="AC26" s="16">
         <v>37.2</v>
       </c>
-      <c r="AD26" s="14">
+      <c r="AD26" s="16">
         <v>10.03</v>
       </c>
-      <c r="AE26" s="14">
+      <c r="AE26" s="16">
         <v>21.77</v>
       </c>
-      <c r="AF26" s="14">
+      <c r="AF26" s="16">
         <v>0.81</v>
       </c>
-      <c r="AG26" s="14">
+      <c r="AG26" s="16">
         <v>42.19</v>
       </c>
-      <c r="AH26" s="14">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="14">
+      <c r="AH26" s="16">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="16">
         <v>77.28</v>
       </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK26" s="18">
+        <v>0.388</v>
+      </c>
+      <c r="AL26" s="16">
+        <v>12.8</v>
+      </c>
+      <c r="AM26" s="16">
+        <v>37.5</v>
+      </c>
+      <c r="AN26" s="16">
+        <v>21.9</v>
+      </c>
+      <c r="AO26" s="16">
+        <v>4.8</v>
+      </c>
+      <c r="AP26" s="16">
+        <v>19.1</v>
+      </c>
+      <c r="AQ26" s="16">
+        <v>14.4</v>
+      </c>
+      <c r="AR26" s="16">
+        <v>12.7</v>
+      </c>
+      <c r="AS26" s="16">
+        <v>27.6</v>
+      </c>
+      <c r="AT26" s="16">
+        <v>37.9</v>
+      </c>
+      <c r="AU26" s="16">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1">
         <v>9450</v>
@@ -4334,10 +5240,10 @@
         <v>3</v>
       </c>
       <c r="T27" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U27" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="V27">
         <v>14</v>
@@ -4384,121 +5290,187 @@
       <c r="AJ27" s="4">
         <v>67.93</v>
       </c>
-    </row>
-    <row r="28" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="11">
+      <c r="AK27" s="5">
+        <v>0.689</v>
+      </c>
+      <c r="AL27" s="4">
+        <v>15.9</v>
+      </c>
+      <c r="AM27" s="4">
+        <v>48.3</v>
+      </c>
+      <c r="AN27" s="4">
+        <v>37.3</v>
+      </c>
+      <c r="AO27" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="AP27" s="4">
+        <v>24.5</v>
+      </c>
+      <c r="AQ27" s="4">
+        <v>25.8</v>
+      </c>
+      <c r="AR27" s="4">
+        <v>27.8</v>
+      </c>
+      <c r="AS27" s="4">
+        <v>38.7</v>
+      </c>
+      <c r="AT27" s="4">
+        <v>48.1</v>
+      </c>
+      <c r="AU27" s="4">
+        <v>63.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="13">
         <v>1678</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="14">
         <v>0.097</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="13">
         <v>17339</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="15">
         <v>1498</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="14">
         <v>1.24</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="16">
         <v>85.51</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="12">
         <v>1</v>
       </c>
-      <c r="J28" s="10">
-        <v>0</v>
-      </c>
-      <c r="K28" s="12">
-        <v>0</v>
-      </c>
-      <c r="L28" s="11">
+      <c r="J28" s="12">
+        <v>0</v>
+      </c>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
         <v>990</v>
       </c>
-      <c r="M28" s="10">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10">
-        <v>0</v>
-      </c>
-      <c r="O28" s="11">
-        <v>0</v>
-      </c>
-      <c r="P28" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="14">
-        <v>0</v>
-      </c>
-      <c r="R28" s="14">
-        <v>0</v>
-      </c>
-      <c r="S28" s="10">
-        <v>0</v>
-      </c>
-      <c r="T28" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10">
-        <v>0</v>
-      </c>
-      <c r="W28" s="11">
+      <c r="M28" s="12">
+        <v>0</v>
+      </c>
+      <c r="N28" s="12">
+        <v>0</v>
+      </c>
+      <c r="O28" s="13">
+        <v>0</v>
+      </c>
+      <c r="P28" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>0</v>
+      </c>
+      <c r="R28" s="16">
+        <v>0</v>
+      </c>
+      <c r="S28" s="12">
+        <v>0</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12">
+        <v>0</v>
+      </c>
+      <c r="W28" s="13">
         <v>560</v>
       </c>
-      <c r="X28" s="14">
+      <c r="X28" s="16">
         <v>82.14</v>
       </c>
-      <c r="Y28" s="14">
+      <c r="Y28" s="16">
         <v>16.61</v>
       </c>
-      <c r="Z28" s="14">
+      <c r="Z28" s="16">
         <v>100</v>
       </c>
-      <c r="AA28" s="14">
+      <c r="AA28" s="16">
         <v>100</v>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="14">
         <v>93.92</v>
       </c>
-      <c r="AC28" s="14">
+      <c r="AC28" s="16">
         <v>68.1</v>
       </c>
-      <c r="AD28" s="14">
+      <c r="AD28" s="16">
         <v>18.3</v>
       </c>
-      <c r="AE28" s="14">
+      <c r="AE28" s="16">
         <v>8.76</v>
       </c>
-      <c r="AF28" s="14">
+      <c r="AF28" s="16">
         <v>29.82</v>
       </c>
-      <c r="AG28" s="14">
+      <c r="AG28" s="16">
         <v>41.96</v>
       </c>
-      <c r="AH28" s="14">
+      <c r="AH28" s="16">
         <v>37.32</v>
       </c>
-      <c r="AI28" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="14">
+      <c r="AI28" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="16">
         <v>70.18</v>
       </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK28" s="18">
+        <v>0.983</v>
+      </c>
+      <c r="AL28" s="16">
+        <v>21.6</v>
+      </c>
+      <c r="AM28" s="16">
+        <v>62</v>
+      </c>
+      <c r="AN28" s="16">
+        <v>60.4</v>
+      </c>
+      <c r="AO28" s="16">
+        <v>11.9</v>
+      </c>
+      <c r="AP28" s="16">
+        <v>32.1</v>
+      </c>
+      <c r="AQ28" s="16">
+        <v>32.2</v>
+      </c>
+      <c r="AR28" s="16">
+        <v>35.9</v>
+      </c>
+      <c r="AS28" s="16">
+        <v>52.4</v>
+      </c>
+      <c r="AT28" s="16">
+        <v>63.1</v>
+      </c>
+      <c r="AU28" s="16">
+        <v>80.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1">
         <v>7427</v>
@@ -4552,10 +5524,10 @@
         <v>1</v>
       </c>
       <c r="T29" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U29" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="V29">
         <v>27</v>
@@ -4602,123 +5574,189 @@
       <c r="AJ29" s="4">
         <v>70.24</v>
       </c>
-    </row>
-    <row r="30" spans="1:36" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="11">
+      <c r="AK29" s="5">
+        <v>0.414</v>
+      </c>
+      <c r="AL29" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="AM29" s="4">
+        <v>31.9</v>
+      </c>
+      <c r="AN29" s="4">
+        <v>26.8</v>
+      </c>
+      <c r="AO29" s="4">
+        <v>6.5</v>
+      </c>
+      <c r="AP29" s="4">
+        <v>20.4</v>
+      </c>
+      <c r="AQ29" s="4">
+        <v>14.8</v>
+      </c>
+      <c r="AR29" s="4">
+        <v>15.1</v>
+      </c>
+      <c r="AS29" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="AT29" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="AU29" s="4">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:47" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="13">
         <v>5672</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="14">
         <v>0.4479</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="13">
         <v>12692</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="15">
         <v>4380</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="14">
         <v>3.61</v>
       </c>
-      <c r="H30" s="14">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10">
-        <v>0</v>
-      </c>
-      <c r="J30" s="10">
+      <c r="H30" s="16">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12">
         <v>1</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="14">
         <v>1.76</v>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="13">
         <v>260</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="12">
         <v>5</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N30" s="12">
         <v>7</v>
       </c>
-      <c r="O30" s="11">
+      <c r="O30" s="13">
         <v>474</v>
       </c>
-      <c r="P30" s="14">
+      <c r="P30" s="16">
         <v>83.57</v>
       </c>
-      <c r="Q30" s="14">
+      <c r="Q30" s="16">
         <v>0.06</v>
       </c>
-      <c r="R30" s="14">
+      <c r="R30" s="16">
         <v>0.05</v>
       </c>
-      <c r="S30" s="10">
-        <v>0</v>
-      </c>
-      <c r="T30" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="U30" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="V30" s="10">
+      <c r="S30" s="12">
+        <v>0</v>
+      </c>
+      <c r="T30" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="U30" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="V30" s="12">
         <v>19</v>
       </c>
-      <c r="W30" s="11">
+      <c r="W30" s="13">
         <v>2227</v>
       </c>
-      <c r="X30" s="14">
+      <c r="X30" s="16">
         <v>99.69</v>
       </c>
-      <c r="Y30" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="14">
+      <c r="Y30" s="16">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="16">
         <v>99.96</v>
       </c>
-      <c r="AA30" s="14">
+      <c r="AA30" s="16">
         <v>99.73</v>
       </c>
-      <c r="AB30" s="12">
+      <c r="AB30" s="14">
         <v>99.58</v>
       </c>
-      <c r="AC30" s="14">
+      <c r="AC30" s="16">
         <v>27.99</v>
       </c>
-      <c r="AD30" s="14">
+      <c r="AD30" s="16">
         <v>6.7</v>
       </c>
-      <c r="AE30" s="14">
+      <c r="AE30" s="16">
         <v>23.24</v>
       </c>
-      <c r="AF30" s="14">
+      <c r="AF30" s="16">
         <v>0.76</v>
       </c>
-      <c r="AG30" s="14">
+      <c r="AG30" s="16">
         <v>34.71</v>
       </c>
-      <c r="AH30" s="14">
+      <c r="AH30" s="16">
         <v>2.65</v>
       </c>
-      <c r="AI30" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="14">
+      <c r="AI30" s="16">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="16">
         <v>81.63</v>
       </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK30" s="18">
+        <v>0.198</v>
+      </c>
+      <c r="AL30" s="16">
+        <v>7.1</v>
+      </c>
+      <c r="AM30" s="16">
+        <v>28.4</v>
+      </c>
+      <c r="AN30" s="16">
+        <v>13.5</v>
+      </c>
+      <c r="AO30" s="16">
+        <v>2.7</v>
+      </c>
+      <c r="AP30" s="16">
+        <v>11.2</v>
+      </c>
+      <c r="AQ30" s="16">
+        <v>13.1</v>
+      </c>
+      <c r="AR30" s="16">
+        <v>8.2</v>
+      </c>
+      <c r="AS30" s="16">
+        <v>21.5</v>
+      </c>
+      <c r="AT30" s="16">
+        <v>30.1</v>
+      </c>
+      <c r="AU30" s="16">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1">
         <v>3200</v>
@@ -4772,10 +5810,10 @@
         <v>2</v>
       </c>
       <c r="T31" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="U31" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="V31">
         <v>21</v>
@@ -4822,9 +5860,42 @@
       <c r="AJ31" s="4">
         <v>97.03</v>
       </c>
+      <c r="AK31" s="5">
+        <v>0.399</v>
+      </c>
+      <c r="AL31" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="AM31" s="4">
+        <v>38.5</v>
+      </c>
+      <c r="AN31" s="4">
+        <v>24.1</v>
+      </c>
+      <c r="AO31" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="AP31" s="4">
+        <v>20.2</v>
+      </c>
+      <c r="AQ31" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="AR31" s="4">
+        <v>14.9</v>
+      </c>
+      <c r="AS31" s="4">
+        <v>28.1</v>
+      </c>
+      <c r="AT31" s="4">
+        <v>39.1</v>
+      </c>
+      <c r="AU31" s="4">
+        <v>36.4</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ1"/>
+  <autoFilter ref="A1:AU1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -4840,240 +5911,240 @@
     <col min="3" max="3" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="12">
+    <row r="1" ht="34" customHeight="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="14">
         <v>-0.93</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>81</v>
+      <c r="C2" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2">
         <v>-0.93</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="12">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="14">
         <v>0.87</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>84</v>
+      <c r="C4" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2">
         <v>0.87</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="14">
         <v>-0.64</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>81</v>
+      <c r="C6" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B7" s="2">
         <v>0.63</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="14">
         <v>0.57</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>84</v>
+      <c r="C8" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B9" s="2">
         <v>-0.56</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="12">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="14">
         <v>-0.54</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>81</v>
+      <c r="C10" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B11" s="2">
         <v>-0.48</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B12" s="12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" s="14">
         <v>-0.48</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>92</v>
+      <c r="C12" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2">
         <v>-0.44</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="14">
         <v>0.37</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>96</v>
+      <c r="C14" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B15" s="2">
         <v>-0.3</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="12">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="14">
         <v>0.3</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>96</v>
+      <c r="C16" s="12" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B17" s="2">
         <v>-0.2</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" s="12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="14">
         <v>-0.13</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>100</v>
+      <c r="C18" s="12" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B19" s="2">
         <v>0.13</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="12">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="14">
         <v>-0.13</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>106</v>
+      <c r="C20" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5097,64 +6168,64 @@
     <col min="7" max="7" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="10">
+    <row r="1" ht="34" customHeight="1" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="12">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>118</v>
+      <c r="F2" s="12">
+        <v>0</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5163,44 +6234,44 @@
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
         <v>50</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>118</v>
+      <c r="G4" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5209,44 +6280,44 @@
         <v>45</v>
       </c>
       <c r="G5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="12">
         <v>44</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="12">
         <v>5</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>118</v>
+      <c r="G6" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E7">
         <v>33</v>
@@ -5255,44 +6326,44 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="12">
         <v>11</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="12">
         <v>29</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>120</v>
+      <c r="G8" s="12" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -5301,44 +6372,44 @@
         <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="12">
         <v>33</v>
       </c>
-      <c r="F10" s="10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>118</v>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -5347,44 +6418,44 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E12" s="12">
         <v>13</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="12">
         <v>1</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>118</v>
+      <c r="G12" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>14</v>
@@ -5393,44 +6464,44 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="12">
         <v>1</v>
       </c>
-      <c r="F14" s="10">
-        <v>0</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>118</v>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>25</v>
@@ -5439,44 +6510,44 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="12">
         <v>31</v>
       </c>
-      <c r="F16" s="10">
-        <v>0</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>118</v>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>36</v>
@@ -5485,44 +6556,44 @@
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="12">
         <v>50</v>
       </c>
-      <c r="F18" s="10">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>118</v>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
         <v>127</v>
       </c>
-      <c r="B19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>116</v>
-      </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>21</v>
@@ -5531,44 +6602,44 @@
         <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="10">
+      <c r="E20" s="12">
         <v>27</v>
       </c>
-      <c r="F20" s="10">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>118</v>
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
         <v>128</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" t="s">
-        <v>117</v>
       </c>
       <c r="E21">
         <v>24</v>
@@ -5577,44 +6648,44 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" s="10">
+    </row>
+    <row r="22" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="12">
         <v>14</v>
       </c>
-      <c r="F22" s="10">
-        <v>0</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>118</v>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>30</v>
@@ -5623,44 +6694,44 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="E24" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E24" s="12">
         <v>18</v>
       </c>
-      <c r="F24" s="10">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>118</v>
+      <c r="F24" s="12">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E25">
         <v>13</v>
@@ -5669,44 +6740,44 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="12">
         <v>27</v>
       </c>
-      <c r="F26" s="10">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>118</v>
+      <c r="F26" s="12">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>19</v>
@@ -5715,30 +6786,30 @@
         <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="12">
         <v>21</v>
       </c>
-      <c r="F28" s="10">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>118</v>
+      <c r="F28" s="12">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -5760,46 +6831,46 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="11">
+    <row r="1" ht="34" customHeight="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="13">
         <v>28</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <v>2</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1">
         <v>72</v>
@@ -5811,29 +6882,29 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="11">
+    <row r="4" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="13">
         <v>56</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="12">
         <v>2</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="12">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C5" s="1">
         <v>144</v>
@@ -5845,29 +6916,29 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="11">
+    <row r="6" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="13">
         <v>80</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="12">
         <v>2</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="12">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1">
         <v>72</v>
@@ -5879,29 +6950,29 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="11">
+    <row r="8" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="13">
         <v>80</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="12">
         <v>2</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="12">
         <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C9" s="1">
         <v>117</v>
@@ -5913,29 +6984,29 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="11">
+    <row r="10" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="13">
         <v>96</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="12">
         <v>2</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="12">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C11" s="1">
         <v>41</v>
@@ -5947,29 +7018,29 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="11">
+    <row r="12" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="13">
         <v>24</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="12">
         <v>2</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="12">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C13" s="1">
         <v>118</v>
@@ -5981,29 +7052,29 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="C14" s="11">
+    <row r="14" spans="1:5" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="13">
         <v>110</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="12">
         <v>2</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="12">
         <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C15" s="1">
         <v>31</v>
@@ -6032,174 +7103,174 @@
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="10">
+    <row r="1" ht="34" customHeight="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="12">
         <v>30</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>171</v>
+      <c r="D2" s="12" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C3">
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" s="12">
         <v>30</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>171</v>
+      <c r="D4" s="12" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C5">
         <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="12">
         <v>330</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>180</v>
+      <c r="D6" s="12" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="C7">
         <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" s="10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="12">
         <v>155</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>183</v>
+      <c r="D8" s="12" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="C9">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="10">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="12">
         <v>14</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>191</v>
+      <c r="D10" s="12" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="C11">
         <v>452</v>
       </c>
       <c r="D11" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>197</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -6218,1530 +7289,1530 @@
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>202</v>
+    <row r="1" ht="34" customHeight="1" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D7" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>213</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B25" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C25" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D27" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B29" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C29" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B35" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="D35" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B37" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C37" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C39" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="D39" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C41" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B43" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="C43" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C45" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B49" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C49" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="D49" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>202</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C51" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D51" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="B53" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C53" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B55" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C57" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D57" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C59" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B61" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B63" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C63" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D63" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C65" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B67" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C67" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D67" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B69" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="D69" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="C72" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B73" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="C73" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D73" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>202</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B75" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C75" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B77" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C77" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D77" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B78" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B79" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C79" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="B81" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C81" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="D81" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B83" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C83" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C87" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D87" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>202</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B89" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C89" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>295</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C91" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B93" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C93" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D93" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B94" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="C95" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B97" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C97" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="D97" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C99" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B101" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C101" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="D101" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>202</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B103" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C103" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D105" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B107" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C107" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>202</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B109" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C109" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="D109" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
